--- a/data/source/weekly/cs-en-us-pbms.xlsx
+++ b/data/source/weekly/cs-en-us-pbms.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -851,369 +851,369 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
+      <c r="E14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="E14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>2</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L14" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="M14" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>-62.5</v>
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G15" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H15" s="15">
-        <v>-26.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J15" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K15" s="15">
-        <v>-30</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L15" s="15">
-        <v>-6.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>27.272727272727</v>
+        <v>38.461538461538</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-41.935483870967</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D16" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E16" s="15">
-        <v>-26.923076923076</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F16" s="14">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G16" s="14">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H16" s="15">
-        <v>-11.340206185567</v>
+        <v>-23.300970873786</v>
       </c>
       <c r="I16" s="14">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="J16" s="14">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="K16" s="15">
-        <v>-11.510791366906</v>
+        <v>-14.457831325301</v>
       </c>
       <c r="L16" s="15">
-        <v>-23.602484472049</v>
+        <v>-21.111111111111</v>
       </c>
       <c r="M16" s="15">
-        <v>-14.583333333333</v>
+        <v>-8.387096774193</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.515406162465</v>
+        <v>-88.511326860841</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D17" s="14">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E17" s="15">
-        <v>-15.217391304347</v>
+        <v>12.5</v>
       </c>
       <c r="F17" s="14">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G17" s="14">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H17" s="15">
-        <v>-1.418439716312</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="J17" s="14">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="K17" s="15">
-        <v>14.795918367346</v>
+        <v>14.912280701754</v>
       </c>
       <c r="L17" s="15">
-        <v>12.5</v>
+        <v>7.377049180327</v>
       </c>
       <c r="M17" s="15">
-        <v>84.426229508196</v>
+        <v>84.507042253521</v>
       </c>
       <c r="N17" s="15">
-        <v>-31.402439024390</v>
+        <v>-30.133333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D18" s="14">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" s="15">
-        <v>-15.151515151515</v>
+        <v>-21.875</v>
       </c>
       <c r="F18" s="14">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="G18" s="14">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="H18" s="15">
-        <v>-14.705882352941</v>
+        <v>-19.496855345911</v>
       </c>
       <c r="I18" s="14">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="J18" s="14">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="K18" s="15">
-        <v>-14.592274678111</v>
+        <v>-13.962264150943</v>
       </c>
       <c r="L18" s="15">
-        <v>-5.687203791469</v>
+        <v>-6.557377049180</v>
       </c>
       <c r="M18" s="15">
-        <v>-20.4</v>
+        <v>-22.972972972973</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.714285714285</v>
+        <v>-85.459183673469</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
         <v>168</v>
       </c>
       <c r="D19" s="14">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E19" s="15">
-        <v>-12.953367875647</v>
+        <v>-9.189189189189</v>
       </c>
       <c r="F19" s="14">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="G19" s="14">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="H19" s="15">
-        <v>-4.781997187060</v>
+        <v>-5.428571428571</v>
       </c>
       <c r="I19" s="14">
-        <v>987</v>
+        <v>1153</v>
       </c>
       <c r="J19" s="14">
-        <v>1045</v>
+        <v>1230</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.550239234449</v>
+        <v>-6.260162601626</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.336683417085</v>
+        <v>-15.839416058394</v>
       </c>
       <c r="M19" s="15">
-        <v>-11.479820627802</v>
+        <v>-10.411810411810</v>
       </c>
       <c r="N19" s="15">
-        <v>-71.341463414634</v>
+        <v>-71.015585721468</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G20" s="14">
         <v>20</v>
       </c>
       <c r="H20" s="15">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J20" s="14">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K20" s="15">
-        <v>-23.076923076923</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="L20" s="15">
-        <v>-58.333333333333</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="M20" s="15">
-        <v>-31.034482758620</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.126436781609</v>
+        <v>-97.132616487455</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" s="17">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.483870967741</v>
+        <v>-9.440559440559</v>
       </c>
       <c r="F21" s="17">
-        <v>1074</v>
+        <v>1037</v>
       </c>
       <c r="G21" s="17">
-        <v>1156</v>
+        <v>1135</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.093425605536</v>
+        <v>-8.634361233480</v>
       </c>
       <c r="I21" s="17">
-        <v>1568</v>
+        <v>1828</v>
       </c>
       <c r="J21" s="17">
-        <v>1661</v>
+        <v>1947</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.599036724864</v>
+        <v>-6.111967128916</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.410480349345</v>
+        <v>-13.446969696969</v>
       </c>
       <c r="M21" s="18">
-        <v>-6.332138590203</v>
+        <v>-5.480868665977</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.506813943480</v>
+        <v>-77.252364360378</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E22" s="15">
-        <v>-17.647058823529</v>
+        <v>-35</v>
       </c>
       <c r="F22" s="14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G22" s="14">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H22" s="15">
-        <v>-11.111111111111</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="I22" s="14">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="J22" s="14">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="K22" s="15">
-        <v>-1.470588235294</v>
+        <v>-6.818181818181</v>
       </c>
       <c r="L22" s="15">
-        <v>-12.987012987013</v>
+        <v>-9.890109890109</v>
       </c>
       <c r="M22" s="15">
-        <v>-4.285714285714</v>
+        <v>2.5</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>-25</v>
+        <v>75</v>
       </c>
       <c r="F23" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G23" s="14">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H23" s="15">
-        <v>-13.953488372093</v>
+        <v>31.034482758620</v>
       </c>
       <c r="I23" s="14">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="J23" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K23" s="15">
-        <v>-3.921568627450</v>
+        <v>5.454545454545</v>
       </c>
       <c r="L23" s="15">
-        <v>58.064516129032</v>
+        <v>45</v>
       </c>
       <c r="M23" s="15">
-        <v>28.947368421052</v>
+        <v>41.463414634146</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="D24" s="14">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E24" s="15">
-        <v>0.277777777777</v>
+        <v>5.882352941176</v>
       </c>
       <c r="F24" s="14">
-        <v>1490</v>
+        <v>1447</v>
       </c>
       <c r="G24" s="14">
-        <v>1563</v>
+        <v>1522</v>
       </c>
       <c r="H24" s="15">
-        <v>-4.670505438259</v>
+        <v>-4.927726675427</v>
       </c>
       <c r="I24" s="14">
-        <v>1980</v>
+        <v>2349</v>
       </c>
       <c r="J24" s="14">
-        <v>2115</v>
+        <v>2472</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.382978723404</v>
+        <v>-4.975728155339</v>
       </c>
       <c r="L24" s="15">
-        <v>-9.049150206706</v>
+        <v>-9.514637904468</v>
       </c>
       <c r="M24" s="15">
-        <v>17.787031528851</v>
+        <v>21.395348837209</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D25" s="14">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="E25" s="15">
-        <v>-6.269592476489</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="F25" s="14">
-        <v>1192</v>
+        <v>1164</v>
       </c>
       <c r="G25" s="14">
-        <v>1285</v>
+        <v>1292</v>
       </c>
       <c r="H25" s="15">
-        <v>-7.237354085603</v>
+        <v>-9.907120743034</v>
       </c>
       <c r="I25" s="14">
-        <v>1594</v>
+        <v>1898</v>
       </c>
       <c r="J25" s="14">
-        <v>1716</v>
+        <v>2028</v>
       </c>
       <c r="K25" s="15">
-        <v>-7.109557109557</v>
+        <v>-6.410256410256</v>
       </c>
       <c r="L25" s="15">
-        <v>-13.510580575149</v>
+        <v>-13.727272727272</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="D26" s="14">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E26" s="15">
-        <v>-13.333333333333</v>
+        <v>26.25</v>
       </c>
       <c r="F26" s="14">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="G26" s="14">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.284023668639</v>
+        <v>1.533742331288</v>
       </c>
       <c r="I26" s="14">
-        <v>454</v>
+        <v>554</v>
       </c>
       <c r="J26" s="14">
-        <v>464</v>
+        <v>544</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.155172413793</v>
+        <v>1.838235294117</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.416666666666</v>
+        <v>-4.482758620689</v>
       </c>
       <c r="M26" s="15">
-        <v>31.213872832369</v>
+        <v>33.173076923076</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>-50</v>
+        <v>150</v>
       </c>
       <c r="F27" s="14">
+        <v>17</v>
+      </c>
+      <c r="G27" s="14">
         <v>15</v>
       </c>
-      <c r="G27" s="14">
-        <v>16</v>
-      </c>
       <c r="H27" s="15">
-        <v>-6.25</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J27" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K27" s="15">
-        <v>-18.181818181818</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>-25</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,163 +1426,163 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D28" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G28" s="14">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H28" s="15">
-        <v>-18.333333333333</v>
+        <v>3.846153846153</v>
       </c>
       <c r="I28" s="14">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J28" s="14">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="K28" s="15">
-        <v>7.042253521126</v>
+        <v>4.651162790697</v>
       </c>
       <c r="L28" s="15">
-        <v>5.555555555555</v>
+        <v>13.924050632911</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
         <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>2</v>
       </c>
       <c r="D31" s="14">
         <v>1</v>
       </c>
       <c r="E31" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G31" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H31" s="15">
-        <v>-60</v>
+        <v>37.5</v>
       </c>
       <c r="I31" s="14">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J31" s="14">
         <v>13</v>
       </c>
       <c r="K31" s="15">
-        <v>-69.230769230769</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L31" s="15">
-        <v>-42.857142857142</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1616,32 +1616,32 @@
       <c r="E33" s="15">
         <v>-100</v>
       </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
       </c>
       <c r="J33" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L33" s="15">
         <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>207</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>14866</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>3997</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>16090</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>44811</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>9446</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>89541</v>

--- a/data/source/weekly/cs-en-us-pbms.xlsx
+++ b/data/source/weekly/cs-en-us-pbms.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -879,13 +879,13 @@
         <v>-50</v>
       </c>
       <c r="L14" s="15">
+        <v>-80</v>
+      </c>
+      <c r="M14" s="15">
         <v>-75</v>
       </c>
-      <c r="M14" s="15">
-        <v>-66.666666666666</v>
-      </c>
       <c r="N14" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G15" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I15" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J15" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K15" s="15">
-        <v>-18.181818181818</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>4.545454545454</v>
       </c>
       <c r="M15" s="15">
-        <v>38.461538461538</v>
+        <v>76.923076923076</v>
       </c>
       <c r="N15" s="15">
-        <v>-41.935483870967</v>
+        <v>-34.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D16" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E16" s="15">
-        <v>-22.222222222222</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="F16" s="14">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G16" s="14">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H16" s="15">
-        <v>-23.300970873786</v>
+        <v>-19.607843137254</v>
       </c>
       <c r="I16" s="14">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="J16" s="14">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="K16" s="15">
-        <v>-14.457831325301</v>
+        <v>-15.228426395939</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.111111111111</v>
+        <v>-19.323671497584</v>
       </c>
       <c r="M16" s="15">
-        <v>-8.387096774193</v>
+        <v>-6.179775280898</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.511326860841</v>
+        <v>-88.239436619718</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D17" s="14">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E17" s="15">
-        <v>12.5</v>
+        <v>14.634146341463</v>
       </c>
       <c r="F17" s="14">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="G17" s="14">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>-1.315789473684</v>
       </c>
       <c r="I17" s="14">
-        <v>262</v>
+        <v>310</v>
       </c>
       <c r="J17" s="14">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="K17" s="15">
-        <v>14.912280701754</v>
+        <v>15.241635687732</v>
       </c>
       <c r="L17" s="15">
-        <v>7.377049180327</v>
+        <v>6.896551724137</v>
       </c>
       <c r="M17" s="15">
-        <v>84.507042253521</v>
+        <v>86.746987951807</v>
       </c>
       <c r="N17" s="15">
-        <v>-30.133333333333</v>
+        <v>-27.738927738927</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D18" s="14">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E18" s="15">
-        <v>-21.875</v>
+        <v>-30.952380952381</v>
       </c>
       <c r="F18" s="14">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="G18" s="14">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="H18" s="15">
-        <v>-19.496855345911</v>
+        <v>-26</v>
       </c>
       <c r="I18" s="14">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="J18" s="14">
-        <v>265</v>
+        <v>307</v>
       </c>
       <c r="K18" s="15">
-        <v>-13.962264150943</v>
+        <v>-15.635179153094</v>
       </c>
       <c r="L18" s="15">
-        <v>-6.557377049180</v>
+        <v>-7.168458781362</v>
       </c>
       <c r="M18" s="15">
-        <v>-22.972972972973</v>
+        <v>-23.372781065088</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.459183673469</v>
+        <v>-85.682697622996</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D19" s="14">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="E19" s="15">
-        <v>-9.189189189189</v>
+        <v>4.458598726114</v>
       </c>
       <c r="F19" s="14">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="G19" s="14">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.428571428571</v>
+        <v>-4.492753623188</v>
       </c>
       <c r="I19" s="14">
-        <v>1153</v>
+        <v>1320</v>
       </c>
       <c r="J19" s="14">
-        <v>1230</v>
+        <v>1387</v>
       </c>
       <c r="K19" s="15">
-        <v>-6.260162601626</v>
+        <v>-4.830569574621</v>
       </c>
       <c r="L19" s="15">
-        <v>-15.839416058394</v>
+        <v>-13.838120104438</v>
       </c>
       <c r="M19" s="15">
-        <v>-10.411810411810</v>
+        <v>-10.447761194029</v>
       </c>
       <c r="N19" s="15">
-        <v>-71.015585721468</v>
+        <v>-70.950704225352</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G20" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H20" s="15">
-        <v>-25</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="I20" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J20" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K20" s="15">
-        <v>-29.411764705882</v>
+        <v>-28.205128205128</v>
       </c>
       <c r="L20" s="15">
-        <v>-53.846153846153</v>
+        <v>-50.877192982456</v>
       </c>
       <c r="M20" s="15">
-        <v>-36.842105263157</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.132616487455</v>
+        <v>-97.027600849256</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="D21" s="17">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="E21" s="18">
-        <v>-9.440559440559</v>
+        <v>-2.846975088967</v>
       </c>
       <c r="F21" s="17">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="G21" s="17">
         <v>1135</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.634361233480</v>
+        <v>-8.722466960352</v>
       </c>
       <c r="I21" s="17">
-        <v>1828</v>
+        <v>2108</v>
       </c>
       <c r="J21" s="17">
-        <v>1947</v>
+        <v>2228</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.111967128916</v>
+        <v>-5.385996409335</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.446969696969</v>
+        <v>-11.872909698996</v>
       </c>
       <c r="M21" s="18">
-        <v>-5.480868665977</v>
+        <v>-4.830699774266</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.252364360378</v>
+        <v>-77.064519638777</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D22" s="14">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E22" s="15">
-        <v>-35</v>
+        <v>50</v>
       </c>
       <c r="F22" s="14">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G22" s="14">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H22" s="15">
-        <v>-10.526315789473</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J22" s="14">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="K22" s="15">
-        <v>-6.818181818181</v>
+        <v>-2.083333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>-9.890109890109</v>
+        <v>-9.615384615384</v>
       </c>
       <c r="M22" s="15">
-        <v>2.5</v>
+        <v>3.296703296703</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F23" s="14">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G23" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H23" s="15">
-        <v>31.034482758620</v>
+        <v>30.769230769230</v>
       </c>
       <c r="I23" s="14">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="J23" s="14">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K23" s="15">
-        <v>5.454545454545</v>
+        <v>9.836065573770</v>
       </c>
       <c r="L23" s="15">
-        <v>45</v>
+        <v>55.813953488372</v>
       </c>
       <c r="M23" s="15">
-        <v>41.463414634146</v>
+        <v>28.846153846153</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="D24" s="14">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="E24" s="15">
-        <v>5.882352941176</v>
+        <v>-9.207161125319</v>
       </c>
       <c r="F24" s="14">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="G24" s="14">
-        <v>1522</v>
+        <v>1507</v>
       </c>
       <c r="H24" s="15">
-        <v>-4.927726675427</v>
+        <v>-4.114134041141</v>
       </c>
       <c r="I24" s="14">
-        <v>2349</v>
+        <v>2698</v>
       </c>
       <c r="J24" s="14">
-        <v>2472</v>
+        <v>2863</v>
       </c>
       <c r="K24" s="15">
-        <v>-4.975728155339</v>
+        <v>-5.763185469786</v>
       </c>
       <c r="L24" s="15">
-        <v>-9.514637904468</v>
+        <v>-10.186418109187</v>
       </c>
       <c r="M24" s="15">
-        <v>21.395348837209</v>
+        <v>20.932317346481</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="D25" s="14">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="E25" s="15">
-        <v>-2.564102564102</v>
+        <v>-17.717717717717</v>
       </c>
       <c r="F25" s="14">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="G25" s="14">
-        <v>1292</v>
+        <v>1265</v>
       </c>
       <c r="H25" s="15">
-        <v>-9.907120743034</v>
+        <v>-8.300395256917</v>
       </c>
       <c r="I25" s="14">
-        <v>1898</v>
+        <v>2175</v>
       </c>
       <c r="J25" s="14">
-        <v>2028</v>
+        <v>2361</v>
       </c>
       <c r="K25" s="15">
-        <v>-6.410256410256</v>
+        <v>-7.878017789072</v>
       </c>
       <c r="L25" s="15">
-        <v>-13.727272727272</v>
+        <v>-14.939382088384</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D26" s="14">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E26" s="15">
-        <v>26.25</v>
+        <v>36.619718309859</v>
       </c>
       <c r="F26" s="14">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="G26" s="14">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="H26" s="15">
-        <v>1.533742331288</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>554</v>
+        <v>651</v>
       </c>
       <c r="J26" s="14">
-        <v>544</v>
+        <v>615</v>
       </c>
       <c r="K26" s="15">
-        <v>1.838235294117</v>
+        <v>5.853658536585</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.482758620689</v>
+        <v>-2.835820895522</v>
       </c>
       <c r="M26" s="15">
-        <v>33.173076923076</v>
+        <v>36.192468619246</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>5</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E27" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G27" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H27" s="15">
-        <v>13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J27" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K27" s="15">
-        <v>-4.166666666666</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="L27" s="15">
-        <v>-17.857142857142</v>
+        <v>-12.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D28" s="14">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E28" s="15">
-        <v>6.666666666666</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F28" s="14">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G28" s="14">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="H28" s="15">
-        <v>3.846153846153</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="I28" s="14">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="J28" s="14">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="K28" s="15">
-        <v>4.651162790697</v>
+        <v>-10.619469026548</v>
       </c>
       <c r="L28" s="15">
-        <v>13.924050632911</v>
+        <v>7.446808510638</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L29" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-95</v>
+        <v>-95.833333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.333333333333</v>
+        <v>-94.736842105263</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1552,31 +1552,31 @@
         <v>2</v>
       </c>
       <c r="D31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="15">
+        <v>0</v>
+      </c>
+      <c r="F31" s="14">
+        <v>14</v>
+      </c>
+      <c r="G31" s="14">
+        <v>7</v>
+      </c>
+      <c r="H31" s="15">
         <v>100</v>
       </c>
-      <c r="F31" s="14">
-        <v>11</v>
-      </c>
-      <c r="G31" s="14">
-        <v>8</v>
-      </c>
-      <c r="H31" s="15">
-        <v>37.5</v>
-      </c>
       <c r="I31" s="14">
+        <v>19</v>
+      </c>
+      <c r="J31" s="14">
         <v>15</v>
       </c>
-      <c r="J31" s="14">
-        <v>13</v>
-      </c>
       <c r="K31" s="15">
-        <v>15.384615384615</v>
+        <v>26.666666666666</v>
       </c>
       <c r="L31" s="15">
-        <v>66.666666666666</v>
+        <v>72.727272727272</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-pbms.xlsx
+++ b/data/source/weekly/cs-en-us-pbms.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
         <v>-80</v>
@@ -885,335 +885,335 @@
         <v>-75</v>
       </c>
       <c r="N14" s="15">
-        <v>-91.666666666666</v>
+        <v>-95.238095238095</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F15" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G15" s="14">
         <v>18</v>
       </c>
       <c r="H15" s="15">
-        <v>-11.111111111111</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I15" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J15" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K15" s="15">
-        <v>-14.814814814814</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>4.545454545454</v>
+        <v>13.636363636363</v>
       </c>
       <c r="M15" s="15">
-        <v>76.923076923076</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-34.285714285714</v>
+        <v>-30.555555555555</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D16" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E16" s="15">
-        <v>-22.580645161290</v>
+        <v>-54.054054054054</v>
       </c>
       <c r="F16" s="14">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G16" s="14">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="H16" s="15">
-        <v>-19.607843137254</v>
+        <v>-33.057851239669</v>
       </c>
       <c r="I16" s="14">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="J16" s="14">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="K16" s="15">
-        <v>-15.228426395939</v>
+        <v>-20.512820512820</v>
       </c>
       <c r="L16" s="15">
-        <v>-19.323671497584</v>
+        <v>-24.081632653061</v>
       </c>
       <c r="M16" s="15">
-        <v>-6.179775280898</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.239436619718</v>
+        <v>-88.403990024937</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
+        <v>35</v>
+      </c>
+      <c r="D17" s="14">
         <v>47</v>
       </c>
-      <c r="D17" s="14">
-        <v>41</v>
-      </c>
       <c r="E17" s="15">
-        <v>14.634146341463</v>
+        <v>-25.531914893617</v>
       </c>
       <c r="F17" s="14">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G17" s="14">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="H17" s="15">
-        <v>-1.315789473684</v>
+        <v>-4.216867469879</v>
       </c>
       <c r="I17" s="14">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="J17" s="14">
-        <v>269</v>
+        <v>316</v>
       </c>
       <c r="K17" s="15">
-        <v>15.241635687732</v>
+        <v>10.759493670886</v>
       </c>
       <c r="L17" s="15">
-        <v>6.896551724137</v>
+        <v>6.707317073170</v>
       </c>
       <c r="M17" s="15">
-        <v>86.746987951807</v>
+        <v>91.256830601092</v>
       </c>
       <c r="N17" s="15">
-        <v>-27.738927738927</v>
+        <v>-27.835051546391</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D18" s="14">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E18" s="15">
-        <v>-30.952380952381</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="F18" s="14">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="G18" s="14">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="H18" s="15">
-        <v>-26</v>
+        <v>-13.103448275862</v>
       </c>
       <c r="I18" s="14">
-        <v>259</v>
+        <v>303</v>
       </c>
       <c r="J18" s="14">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="K18" s="15">
-        <v>-15.635179153094</v>
+        <v>-12.173913043478</v>
       </c>
       <c r="L18" s="15">
-        <v>-7.168458781362</v>
+        <v>-9.281437125748</v>
       </c>
       <c r="M18" s="15">
-        <v>-23.372781065088</v>
+        <v>-21.907216494845</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.682697622996</v>
+        <v>-84.955312810327</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D19" s="14">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="E19" s="15">
-        <v>4.458598726114</v>
+        <v>-19.597989949748</v>
       </c>
       <c r="F19" s="14">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="G19" s="14">
-        <v>690</v>
+        <v>734</v>
       </c>
       <c r="H19" s="15">
-        <v>-4.492753623188</v>
+        <v>-9.945504087193</v>
       </c>
       <c r="I19" s="14">
-        <v>1320</v>
+        <v>1483</v>
       </c>
       <c r="J19" s="14">
-        <v>1387</v>
+        <v>1586</v>
       </c>
       <c r="K19" s="15">
-        <v>-4.830569574621</v>
+        <v>-6.494325346784</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.838120104438</v>
+        <v>-13.122437024018</v>
       </c>
       <c r="M19" s="15">
-        <v>-10.447761194029</v>
+        <v>-8.738461538461</v>
       </c>
       <c r="N19" s="15">
-        <v>-70.950704225352</v>
+        <v>-70.743736437167</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
+        <v>6</v>
+      </c>
+      <c r="D20" s="14">
         <v>4</v>
       </c>
-      <c r="D20" s="14">
-        <v>5</v>
-      </c>
       <c r="E20" s="15">
-        <v>-20</v>
+        <v>50</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G20" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H20" s="15">
-        <v>-22.727272727272</v>
+        <v>-5</v>
       </c>
       <c r="I20" s="14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J20" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K20" s="15">
-        <v>-28.205128205128</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="L20" s="15">
-        <v>-50.877192982456</v>
+        <v>-46.031746031746</v>
       </c>
       <c r="M20" s="15">
-        <v>-33.333333333333</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.027600849256</v>
+        <v>-96.816479400749</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="D21" s="17">
-        <v>281</v>
+        <v>329</v>
       </c>
       <c r="E21" s="18">
-        <v>-2.846975088967</v>
+        <v>-22.188449848024</v>
       </c>
       <c r="F21" s="17">
-        <v>1036</v>
+        <v>1061</v>
       </c>
       <c r="G21" s="17">
-        <v>1135</v>
+        <v>1206</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.722466960352</v>
+        <v>-12.023217247097</v>
       </c>
       <c r="I21" s="17">
-        <v>2108</v>
+        <v>2382</v>
       </c>
       <c r="J21" s="17">
-        <v>2228</v>
+        <v>2557</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.385996409335</v>
+        <v>-6.843957763003</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.872909698996</v>
+        <v>-11.908284023668</v>
       </c>
       <c r="M21" s="18">
-        <v>-4.830699774266</v>
+        <v>-3.131354209028</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.064519638777</v>
+        <v>-76.867048654948</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="14">
+        <v>5</v>
+      </c>
+      <c r="D22" s="14">
+        <v>17</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-70.588235294117</v>
+      </c>
+      <c r="F22" s="14">
+        <v>47</v>
+      </c>
+      <c r="G22" s="14">
+        <v>62</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-24.193548387096</v>
+      </c>
+      <c r="I22" s="14">
+        <v>101</v>
+      </c>
+      <c r="J22" s="14">
+        <v>113</v>
+      </c>
+      <c r="K22" s="15">
+        <v>-10.619469026548</v>
+      </c>
+      <c r="L22" s="15">
+        <v>-10.619469026548</v>
+      </c>
+      <c r="M22" s="15">
+        <v>2.020202020202</v>
+      </c>
+      <c r="N22" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="C22" s="14">
-        <v>12</v>
-      </c>
-      <c r="D22" s="14">
-        <v>8</v>
-      </c>
-      <c r="E22" s="15">
-        <v>50</v>
-      </c>
-      <c r="F22" s="14">
-        <v>52</v>
-      </c>
-      <c r="G22" s="14">
-        <v>52</v>
-      </c>
-      <c r="H22" s="15">
-        <v>0</v>
-      </c>
-      <c r="I22" s="14">
-        <v>94</v>
-      </c>
-      <c r="J22" s="14">
-        <v>96</v>
-      </c>
-      <c r="K22" s="15">
-        <v>-2.083333333333</v>
-      </c>
-      <c r="L22" s="15">
-        <v>-9.615384615384</v>
-      </c>
-      <c r="M22" s="15">
-        <v>3.296703296703</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1224,37 +1224,37 @@
         <v>9</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E23" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G23" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H23" s="15">
-        <v>30.769230769230</v>
+        <v>12.903225806451</v>
       </c>
       <c r="I23" s="14">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J23" s="14">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="K23" s="15">
-        <v>9.836065573770</v>
+        <v>10</v>
       </c>
       <c r="L23" s="15">
-        <v>55.813953488372</v>
+        <v>35.087719298245</v>
       </c>
       <c r="M23" s="15">
-        <v>28.846153846153</v>
+        <v>37.5</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>355</v>
+        <v>295</v>
       </c>
       <c r="D24" s="14">
-        <v>391</v>
+        <v>345</v>
       </c>
       <c r="E24" s="15">
-        <v>-9.207161125319</v>
+        <v>-14.492753623188</v>
       </c>
       <c r="F24" s="14">
-        <v>1445</v>
+        <v>1377</v>
       </c>
       <c r="G24" s="14">
-        <v>1507</v>
+        <v>1453</v>
       </c>
       <c r="H24" s="15">
-        <v>-4.114134041141</v>
+        <v>-5.230557467309</v>
       </c>
       <c r="I24" s="14">
-        <v>2698</v>
+        <v>2982</v>
       </c>
       <c r="J24" s="14">
-        <v>2863</v>
+        <v>3208</v>
       </c>
       <c r="K24" s="15">
-        <v>-5.763185469786</v>
+        <v>-7.044887780548</v>
       </c>
       <c r="L24" s="15">
-        <v>-10.186418109187</v>
+        <v>-14.137633170169</v>
       </c>
       <c r="M24" s="15">
-        <v>20.932317346481</v>
+        <v>20.53354890865</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>274</v>
+        <v>234</v>
       </c>
       <c r="D25" s="14">
-        <v>333</v>
+        <v>304</v>
       </c>
       <c r="E25" s="15">
-        <v>-17.717717717717</v>
+        <v>-23.026315789473</v>
       </c>
       <c r="F25" s="14">
-        <v>1160</v>
+        <v>1112</v>
       </c>
       <c r="G25" s="14">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="H25" s="15">
-        <v>-8.300395256917</v>
+        <v>-12.302839116719</v>
       </c>
       <c r="I25" s="14">
-        <v>2175</v>
+        <v>2406</v>
       </c>
       <c r="J25" s="14">
-        <v>2361</v>
+        <v>2665</v>
       </c>
       <c r="K25" s="15">
-        <v>-7.878017789072</v>
+        <v>-9.718574108818</v>
       </c>
       <c r="L25" s="15">
-        <v>-14.939382088384</v>
+        <v>-18.329938900203</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D26" s="14">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="E26" s="15">
-        <v>36.619718309859</v>
+        <v>-2.247191011235</v>
       </c>
       <c r="F26" s="14">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="G26" s="14">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="H26" s="15">
-        <v>13.333333333333</v>
+        <v>10.606060606060</v>
       </c>
       <c r="I26" s="14">
-        <v>651</v>
+        <v>736</v>
       </c>
       <c r="J26" s="14">
-        <v>615</v>
+        <v>704</v>
       </c>
       <c r="K26" s="15">
-        <v>5.853658536585</v>
+        <v>4.545454545454</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.835820895522</v>
+        <v>-2.645502645502</v>
       </c>
       <c r="M26" s="15">
-        <v>36.192468619246</v>
+        <v>38.086303939962</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="14">
         <v>5</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F27" s="14">
         <v>18</v>
       </c>
       <c r="G27" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="I27" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J27" s="14">
+        <v>34</v>
+      </c>
+      <c r="K27" s="15">
+        <v>-5.882352941176</v>
+      </c>
+      <c r="L27" s="15">
+        <v>-8.571428571428</v>
+      </c>
+      <c r="M27" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="K27" s="15">
-        <v>-3.448275862068</v>
-      </c>
-      <c r="L27" s="15">
-        <v>-12.5</v>
-      </c>
-      <c r="M27" s="13" t="s">
-        <v>21</v>
-      </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D28" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E28" s="15">
-        <v>-55.555555555555</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="F28" s="14">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G28" s="14">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H28" s="15">
-        <v>-30.555555555555</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="J28" s="14">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="K28" s="15">
-        <v>-10.619469026548</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="L28" s="15">
-        <v>7.446808510638</v>
+        <v>-2.654867256637</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1479,19 +1479,19 @@
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
       </c>
       <c r="J29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L29" s="15">
         <v>-66.666666666666</v>
@@ -1500,7 +1500,7 @@
         <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.833333333333</v>
+        <v>-96.296296296296</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1520,19 +1520,19 @@
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
       </c>
       <c r="J30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L30" s="15">
         <v>-66.666666666666</v>
@@ -1541,7 +1541,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.736842105263</v>
+        <v>-95.238095238095</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1552,37 +1552,37 @@
         <v>2</v>
       </c>
       <c r="D31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F31" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G31" s="14">
         <v>7</v>
       </c>
       <c r="H31" s="15">
-        <v>100</v>
+        <v>71.428571428571</v>
       </c>
       <c r="I31" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J31" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K31" s="15">
-        <v>26.666666666666</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L31" s="15">
-        <v>72.727272727272</v>
+        <v>40</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1629,19 +1629,19 @@
         <v>1</v>
       </c>
       <c r="J33" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K33" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L33" s="15">
         <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>207</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>14866</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>3997</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>16090</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>44811</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>9446</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>89541</v>

--- a/data/source/weekly/cs-en-us-pbms.xlsx
+++ b/data/source/weekly/cs-en-us-pbms.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,20 +854,20 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -885,335 +885,335 @@
         <v>-75</v>
       </c>
       <c r="N14" s="15">
-        <v>-95.238095238095</v>
+        <v>-95.652173913043</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="14">
         <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>14</v>
       </c>
       <c r="G15" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H15" s="15">
-        <v>-22.222222222222</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I15" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J15" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K15" s="15">
-        <v>-16.666666666666</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="L15" s="15">
-        <v>13.636363636363</v>
+        <v>7.692307692307</v>
       </c>
       <c r="M15" s="15">
-        <v>66.666666666666</v>
+        <v>86.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-30.555555555555</v>
+        <v>-31.707317073170</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D16" s="14">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E16" s="15">
-        <v>-54.054054054054</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G16" s="14">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.057851239669</v>
+        <v>-31.858407079646</v>
       </c>
       <c r="I16" s="14">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="J16" s="14">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="K16" s="15">
-        <v>-20.512820512820</v>
+        <v>-20.634920634920</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.081632653061</v>
+        <v>-25.093632958801</v>
       </c>
       <c r="M16" s="15">
-        <v>-6.060606060606</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.403990024937</v>
+        <v>-88.980716253443</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" s="14">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E17" s="15">
-        <v>-25.531914893617</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="F17" s="14">
+        <v>156</v>
+      </c>
+      <c r="G17" s="14">
         <v>159</v>
       </c>
-      <c r="G17" s="14">
-        <v>166</v>
-      </c>
       <c r="H17" s="15">
-        <v>-4.216867469879</v>
+        <v>-1.886792452830</v>
       </c>
       <c r="I17" s="14">
-        <v>350</v>
+        <v>387</v>
       </c>
       <c r="J17" s="14">
-        <v>316</v>
+        <v>355</v>
       </c>
       <c r="K17" s="15">
-        <v>10.759493670886</v>
+        <v>9.014084507042</v>
       </c>
       <c r="L17" s="15">
-        <v>6.707317073170</v>
+        <v>4.594594594594</v>
       </c>
       <c r="M17" s="15">
-        <v>91.256830601092</v>
+        <v>85.167464114832</v>
       </c>
       <c r="N17" s="15">
-        <v>-27.835051546391</v>
+        <v>-28.465804066543</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D18" s="14">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E18" s="15">
-        <v>-5.263157894736</v>
+        <v>-51.063829787234</v>
       </c>
       <c r="F18" s="14">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G18" s="14">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="H18" s="15">
-        <v>-13.103448275862</v>
+        <v>-23.899371069182</v>
       </c>
       <c r="I18" s="14">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="J18" s="14">
-        <v>345</v>
+        <v>392</v>
       </c>
       <c r="K18" s="15">
-        <v>-12.173913043478</v>
+        <v>-16.836734693877</v>
       </c>
       <c r="L18" s="15">
-        <v>-9.281437125748</v>
+        <v>-15.104166666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-21.907216494845</v>
+        <v>-23.831775700934</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.955312810327</v>
+        <v>-85.354896675651</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D19" s="14">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="E19" s="15">
-        <v>-19.597989949748</v>
+        <v>-26.291079812206</v>
       </c>
       <c r="F19" s="14">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="G19" s="14">
-        <v>734</v>
+        <v>754</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.945504087193</v>
+        <v>-14.721485411140</v>
       </c>
       <c r="I19" s="14">
-        <v>1483</v>
+        <v>1635</v>
       </c>
       <c r="J19" s="14">
-        <v>1586</v>
+        <v>1799</v>
       </c>
       <c r="K19" s="15">
-        <v>-6.494325346784</v>
+        <v>-9.116175653140</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.122437024018</v>
+        <v>-14.308176100628</v>
       </c>
       <c r="M19" s="15">
-        <v>-8.738461538461</v>
+        <v>-10.410958904109</v>
       </c>
       <c r="N19" s="15">
-        <v>-70.743736437167</v>
+        <v>-70.995210218201</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>50</v>
+        <v>-40</v>
       </c>
       <c r="F20" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H20" s="15">
-        <v>-5</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I20" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J20" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K20" s="15">
-        <v>-20.930232558139</v>
+        <v>-25</v>
       </c>
       <c r="L20" s="15">
-        <v>-46.031746031746</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="M20" s="15">
-        <v>-26.086956521739</v>
+        <v>-32.075471698113</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.816479400749</v>
+        <v>-96.982397317686</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="D21" s="17">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E21" s="18">
-        <v>-22.188449848024</v>
+        <v>-27.692307692307</v>
       </c>
       <c r="F21" s="17">
-        <v>1061</v>
+        <v>1028</v>
       </c>
       <c r="G21" s="17">
-        <v>1206</v>
+        <v>1221</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.023217247097</v>
+        <v>-15.806715806715</v>
       </c>
       <c r="I21" s="17">
-        <v>2382</v>
+        <v>2613</v>
       </c>
       <c r="J21" s="17">
-        <v>2557</v>
+        <v>2882</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.843957763003</v>
+        <v>-9.333795975017</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.908284023668</v>
+        <v>-13.705416116248</v>
       </c>
       <c r="M21" s="18">
-        <v>-3.131354209028</v>
+        <v>-5.119825708061</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.867048654948</v>
+        <v>-77.230742418961</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D22" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E22" s="15">
-        <v>-70.588235294117</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="F22" s="14">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G22" s="14">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H22" s="15">
-        <v>-24.193548387096</v>
+        <v>-39.0625</v>
       </c>
       <c r="I22" s="14">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J22" s="14">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="K22" s="15">
-        <v>-10.619469026548</v>
+        <v>-17.424242424242</v>
       </c>
       <c r="L22" s="15">
-        <v>-10.619469026548</v>
+        <v>-12.096774193548</v>
       </c>
       <c r="M22" s="15">
-        <v>2.020202020202</v>
+        <v>1.869158878504</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="F23" s="14">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G23" s="14">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H23" s="15">
-        <v>12.903225806451</v>
+        <v>10.344827586206</v>
       </c>
       <c r="I23" s="14">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="J23" s="14">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K23" s="15">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="L23" s="15">
-        <v>35.087719298245</v>
+        <v>22.058823529411</v>
       </c>
       <c r="M23" s="15">
-        <v>37.5</v>
+        <v>31.746031746031</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="D24" s="14">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="E24" s="15">
-        <v>-14.492753623188</v>
+        <v>-3.539823008849</v>
       </c>
       <c r="F24" s="14">
-        <v>1377</v>
+        <v>1349</v>
       </c>
       <c r="G24" s="14">
-        <v>1453</v>
+        <v>1432</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.230557467309</v>
+        <v>-5.796089385474</v>
       </c>
       <c r="I24" s="14">
-        <v>2982</v>
+        <v>3309</v>
       </c>
       <c r="J24" s="14">
-        <v>3208</v>
+        <v>3547</v>
       </c>
       <c r="K24" s="15">
-        <v>-7.044887780548</v>
+        <v>-6.709895686495</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.137633170169</v>
+        <v>-14.826254826254</v>
       </c>
       <c r="M24" s="15">
-        <v>20.53354890865</v>
+        <v>20.152505446623</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="D25" s="14">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="E25" s="15">
-        <v>-23.026315789473</v>
+        <v>-5.797101449275</v>
       </c>
       <c r="F25" s="14">
-        <v>1112</v>
+        <v>1072</v>
       </c>
       <c r="G25" s="14">
-        <v>1268</v>
+        <v>1225</v>
       </c>
       <c r="H25" s="15">
-        <v>-12.302839116719</v>
+        <v>-12.489795918367</v>
       </c>
       <c r="I25" s="14">
-        <v>2406</v>
+        <v>2666</v>
       </c>
       <c r="J25" s="14">
-        <v>2665</v>
+        <v>2941</v>
       </c>
       <c r="K25" s="15">
-        <v>-9.718574108818</v>
+        <v>-9.350561033662</v>
       </c>
       <c r="L25" s="15">
-        <v>-18.329938900203</v>
+        <v>-19.529127678840</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D26" s="14">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="E26" s="15">
-        <v>-2.247191011235</v>
+        <v>-12.5</v>
       </c>
       <c r="F26" s="14">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="G26" s="14">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="H26" s="15">
-        <v>10.606060606060</v>
+        <v>10.174418604651</v>
       </c>
       <c r="I26" s="14">
-        <v>736</v>
+        <v>828</v>
       </c>
       <c r="J26" s="14">
-        <v>704</v>
+        <v>808</v>
       </c>
       <c r="K26" s="15">
-        <v>4.545454545454</v>
+        <v>2.475247524752</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.645502645502</v>
+        <v>-3.044496487119</v>
       </c>
       <c r="M26" s="15">
-        <v>38.086303939962</v>
+        <v>35.737704918032</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>3</v>
+      </c>
+      <c r="D27" s="14">
         <v>4</v>
       </c>
-      <c r="D27" s="14">
-        <v>5</v>
-      </c>
       <c r="E27" s="15">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="F27" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G27" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H27" s="15">
-        <v>-10</v>
+        <v>6.25</v>
       </c>
       <c r="I27" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J27" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K27" s="15">
-        <v>-5.882352941176</v>
+        <v>-7.894736842105</v>
       </c>
       <c r="L27" s="15">
-        <v>-8.571428571428</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D28" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E28" s="15">
-        <v>-59.090909090909</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="F28" s="14">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G28" s="14">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>-36.144578313253</v>
       </c>
       <c r="I28" s="14">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="J28" s="14">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="K28" s="15">
-        <v>-18.518518518518</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L28" s="15">
-        <v>-2.654867256637</v>
+        <v>-3.816793893129</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,20 +1469,20 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
@@ -1494,13 +1494,13 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="M29" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.296296296296</v>
+        <v>-96.774193548387</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,20 +1510,20 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
@@ -1535,13 +1535,13 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.238095238095</v>
+        <v>-96</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1549,40 +1549,40 @@
         <v>38</v>
       </c>
       <c r="C31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="14">
         <v>3</v>
       </c>
       <c r="E31" s="15">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F31" s="14">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G31" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H31" s="15">
-        <v>71.428571428571</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I31" s="14">
+        <v>19</v>
+      </c>
+      <c r="J31" s="14">
         <v>21</v>
       </c>
-      <c r="J31" s="14">
-        <v>18</v>
-      </c>
       <c r="K31" s="15">
-        <v>16.666666666666</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="L31" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1610,17 +1610,17 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G33" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33" s="15">
         <v>-100</v>
@@ -1635,13 +1635,13 @@
         <v>-75</v>
       </c>
       <c r="L33" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>207</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>14866</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>3997</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>16090</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>44811</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>9446</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>89541</v>

--- a/data/source/weekly/cs-en-us-pbms.xlsx
+++ b/data/source/weekly/cs-en-us-pbms.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -870,22 +870,22 @@
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="14">
         <v>3</v>
       </c>
       <c r="K14" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="L14" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="L14" s="15">
-        <v>-80</v>
-      </c>
       <c r="M14" s="15">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="N14" s="15">
-        <v>-95.652173913043</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
         <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F15" s="14">
+        <v>12</v>
+      </c>
+      <c r="G15" s="14">
         <v>14</v>
       </c>
-      <c r="G15" s="14">
-        <v>13</v>
-      </c>
       <c r="H15" s="15">
-        <v>7.692307692307</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I15" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J15" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K15" s="15">
-        <v>-15.151515151515</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>7.692307692307</v>
+        <v>-6.25</v>
       </c>
       <c r="M15" s="15">
-        <v>86.666666666666</v>
+        <v>87.5</v>
       </c>
       <c r="N15" s="15">
-        <v>-31.707317073170</v>
+        <v>-31.818181818181</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D16" s="14">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E16" s="15">
-        <v>-16.666666666666</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G16" s="14">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H16" s="15">
-        <v>-31.858407079646</v>
+        <v>-32.758620689655</v>
       </c>
       <c r="I16" s="14">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="J16" s="14">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="K16" s="15">
-        <v>-20.634920634920</v>
+        <v>-20.921985815602</v>
       </c>
       <c r="L16" s="15">
-        <v>-25.093632958801</v>
+        <v>-22.837370242214</v>
       </c>
       <c r="M16" s="15">
-        <v>-9.090909090909</v>
+        <v>-5.106382978723</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.980716253443</v>
+        <v>-88.844422211105</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D17" s="14">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E17" s="15">
-        <v>-12.820512820512</v>
+        <v>-13.461538461538</v>
       </c>
       <c r="F17" s="14">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="G17" s="14">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="H17" s="15">
-        <v>-1.886792452830</v>
+        <v>-4.469273743016</v>
       </c>
       <c r="I17" s="14">
-        <v>387</v>
+        <v>441</v>
       </c>
       <c r="J17" s="14">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="K17" s="15">
-        <v>9.014084507042</v>
+        <v>8.353808353808</v>
       </c>
       <c r="L17" s="15">
-        <v>4.594594594594</v>
+        <v>7.038834951456</v>
       </c>
       <c r="M17" s="15">
-        <v>85.167464114832</v>
+        <v>86.864406779661</v>
       </c>
       <c r="N17" s="15">
-        <v>-28.465804066543</v>
+        <v>-26.5</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D18" s="14">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E18" s="15">
-        <v>-51.063829787234</v>
+        <v>-11.363636363636</v>
       </c>
       <c r="F18" s="14">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="G18" s="14">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="H18" s="15">
-        <v>-23.899371069182</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I18" s="14">
-        <v>326</v>
+        <v>367</v>
       </c>
       <c r="J18" s="14">
-        <v>392</v>
+        <v>436</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.836734693877</v>
+        <v>-15.825688073394</v>
       </c>
       <c r="L18" s="15">
-        <v>-15.104166666666</v>
+        <v>-13.033175355450</v>
       </c>
       <c r="M18" s="15">
-        <v>-23.831775700934</v>
+        <v>-19.162995594713</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.354896675651</v>
+        <v>-84.701959149645</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D19" s="14">
-        <v>213</v>
+        <v>185</v>
       </c>
       <c r="E19" s="15">
-        <v>-26.291079812206</v>
+        <v>-7.567567567567</v>
       </c>
       <c r="F19" s="14">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G19" s="14">
         <v>754</v>
       </c>
       <c r="H19" s="15">
-        <v>-14.721485411140</v>
+        <v>-14.190981432360</v>
       </c>
       <c r="I19" s="14">
-        <v>1635</v>
+        <v>1808</v>
       </c>
       <c r="J19" s="14">
-        <v>1799</v>
+        <v>1984</v>
       </c>
       <c r="K19" s="15">
-        <v>-9.116175653140</v>
+        <v>-8.870967741935</v>
       </c>
       <c r="L19" s="15">
-        <v>-14.308176100628</v>
+        <v>-14.027579648121</v>
       </c>
       <c r="M19" s="15">
-        <v>-10.410958904109</v>
+        <v>-9.191361125062</v>
       </c>
       <c r="N19" s="15">
-        <v>-70.995210218201</v>
+        <v>-70.524942940984</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
         <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-40</v>
+        <v>60</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H20" s="15">
-        <v>-27.272727272727</v>
+        <v>5.263157894736</v>
       </c>
       <c r="I20" s="14">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J20" s="14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K20" s="15">
-        <v>-25</v>
+        <v>-16.981132075471</v>
       </c>
       <c r="L20" s="15">
-        <v>-47.058823529411</v>
+        <v>-45</v>
       </c>
       <c r="M20" s="15">
-        <v>-32.075471698113</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.982397317686</v>
+        <v>-96.538158929976</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>235</v>
+        <v>289</v>
       </c>
       <c r="D21" s="17">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="E21" s="18">
-        <v>-27.692307692307</v>
+        <v>-9.404388714733</v>
       </c>
       <c r="F21" s="17">
-        <v>1028</v>
+        <v>1064</v>
       </c>
       <c r="G21" s="17">
-        <v>1221</v>
+        <v>1254</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.806715806715</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="I21" s="17">
-        <v>2613</v>
+        <v>2915</v>
       </c>
       <c r="J21" s="17">
-        <v>2882</v>
+        <v>3201</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.333795975017</v>
+        <v>-8.934707903780</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.705416116248</v>
+        <v>-12.828947368421</v>
       </c>
       <c r="M21" s="18">
-        <v>-5.119825708061</v>
+        <v>-2.671118530884</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.230742418961</v>
+        <v>-76.627645926876</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D22" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E22" s="15">
-        <v>-63.157894736842</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F22" s="14">
         <v>39</v>
       </c>
       <c r="G22" s="14">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H22" s="15">
-        <v>-39.0625</v>
+        <v>-40</v>
       </c>
       <c r="I22" s="14">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="J22" s="14">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="K22" s="15">
-        <v>-17.424242424242</v>
+        <v>-18.300653594771</v>
       </c>
       <c r="L22" s="15">
-        <v>-12.096774193548</v>
+        <v>-8.759124087591</v>
       </c>
       <c r="M22" s="15">
-        <v>1.869158878504</v>
+        <v>6.837606837606</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D23" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" s="15">
-        <v>-30</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F23" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G23" s="14">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H23" s="15">
-        <v>10.344827586206</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I23" s="14">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="J23" s="14">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K23" s="15">
-        <v>3.75</v>
+        <v>5.494505494505</v>
       </c>
       <c r="L23" s="15">
-        <v>22.058823529411</v>
+        <v>23.076923076923</v>
       </c>
       <c r="M23" s="15">
-        <v>31.746031746031</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D24" s="14">
-        <v>339</v>
+        <v>366</v>
       </c>
       <c r="E24" s="15">
-        <v>-3.539823008849</v>
+        <v>-10.382513661202</v>
       </c>
       <c r="F24" s="14">
-        <v>1349</v>
+        <v>1293</v>
       </c>
       <c r="G24" s="14">
-        <v>1432</v>
+        <v>1441</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.796089385474</v>
+        <v>-10.270645385149</v>
       </c>
       <c r="I24" s="14">
-        <v>3309</v>
+        <v>3629</v>
       </c>
       <c r="J24" s="14">
-        <v>3547</v>
+        <v>3913</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.709895686495</v>
+        <v>-7.257858420649</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.826254826254</v>
+        <v>-15.545729578775</v>
       </c>
       <c r="M24" s="15">
-        <v>20.152505446623</v>
+        <v>20.205366015236</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="D25" s="14">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="E25" s="15">
-        <v>-5.797101449275</v>
+        <v>-20.792079207920</v>
       </c>
       <c r="F25" s="14">
-        <v>1072</v>
+        <v>1002</v>
       </c>
       <c r="G25" s="14">
-        <v>1225</v>
+        <v>1216</v>
       </c>
       <c r="H25" s="15">
-        <v>-12.489795918367</v>
+        <v>-17.598684210526</v>
       </c>
       <c r="I25" s="14">
-        <v>2666</v>
+        <v>2903</v>
       </c>
       <c r="J25" s="14">
-        <v>2941</v>
+        <v>3244</v>
       </c>
       <c r="K25" s="15">
-        <v>-9.350561033662</v>
+        <v>-10.511713933415</v>
       </c>
       <c r="L25" s="15">
-        <v>-19.529127678840</v>
+        <v>-20.899182561307</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D26" s="14">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E26" s="15">
-        <v>-12.5</v>
+        <v>7.608695652173</v>
       </c>
       <c r="F26" s="14">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="G26" s="14">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="H26" s="15">
-        <v>10.174418604651</v>
+        <v>3.370786516853</v>
       </c>
       <c r="I26" s="14">
-        <v>828</v>
+        <v>916</v>
       </c>
       <c r="J26" s="14">
-        <v>808</v>
+        <v>900</v>
       </c>
       <c r="K26" s="15">
-        <v>2.475247524752</v>
+        <v>1.777777777777</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.044496487119</v>
+        <v>-4.184100418410</v>
       </c>
       <c r="M26" s="15">
-        <v>35.737704918032</v>
+        <v>33.527696793002</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>3</v>
       </c>
       <c r="D27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E27" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F27" s="14">
+        <v>15</v>
+      </c>
+      <c r="G27" s="14">
+        <v>20</v>
+      </c>
+      <c r="H27" s="15">
         <v>-25</v>
       </c>
-      <c r="F27" s="14">
-        <v>17</v>
-      </c>
-      <c r="G27" s="14">
-        <v>16</v>
-      </c>
-      <c r="H27" s="15">
-        <v>6.25</v>
-      </c>
       <c r="I27" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J27" s="14">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K27" s="15">
-        <v>-7.894736842105</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="L27" s="15">
-        <v>-16.666666666666</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>16</v>
       </c>
       <c r="D28" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E28" s="15">
-        <v>-15.789473684210</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G28" s="14">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H28" s="15">
-        <v>-36.144578313253</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I28" s="14">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="J28" s="14">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="K28" s="15">
-        <v>-18.181818181818</v>
+        <v>-15.882352941176</v>
       </c>
       <c r="L28" s="15">
-        <v>-3.816793893129</v>
+        <v>-7.741935483870</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,14 +1475,14 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
@@ -1500,7 +1500,7 @@
         <v>-80</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.774193548387</v>
+        <v>-96.969696969697</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,14 +1516,14 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="14">
         <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
@@ -1541,7 +1541,7 @@
         <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-96</v>
+        <v>-96.296296296296</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1552,31 +1552,31 @@
         <v>1</v>
       </c>
       <c r="D31" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F31" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G31" s="14">
         <v>9</v>
       </c>
       <c r="H31" s="15">
-        <v>-44.444444444444</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I31" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J31" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K31" s="15">
-        <v>-9.523809523809</v>
+        <v>4.545454545454</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>4.545454545454</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1620,7 +1620,7 @@
         <v>20</v>
       </c>
       <c r="G33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-pbms.xlsx
+++ b/data/source/weekly/cs-en-us-pbms.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -885,7 +885,7 @@
         <v>-60</v>
       </c>
       <c r="N14" s="15">
-        <v>-92</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,37 +896,37 @@
         <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E15" s="15">
-        <v>-33.333333333333</v>
+        <v>-80</v>
       </c>
       <c r="F15" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G15" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H15" s="15">
-        <v>-14.285714285714</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="I15" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J15" s="14">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="K15" s="15">
-        <v>-16.666666666666</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="L15" s="15">
-        <v>-6.25</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M15" s="15">
-        <v>87.5</v>
+        <v>88.235294117647</v>
       </c>
       <c r="N15" s="15">
-        <v>-31.818181818181</v>
+        <v>-30.434782608695</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D16" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E16" s="15">
-        <v>-23.333333333333</v>
+        <v>-53.125</v>
       </c>
       <c r="F16" s="14">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="G16" s="14">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H16" s="15">
-        <v>-32.758620689655</v>
+        <v>-41.880341880341</v>
       </c>
       <c r="I16" s="14">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="J16" s="14">
-        <v>282</v>
+        <v>314</v>
       </c>
       <c r="K16" s="15">
-        <v>-20.921985815602</v>
+        <v>-24.840764331210</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.837370242214</v>
+        <v>-25.316455696202</v>
       </c>
       <c r="M16" s="15">
-        <v>-5.106382978723</v>
+        <v>-7.450980392156</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.844422211105</v>
+        <v>-89.199084668192</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D17" s="14">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E17" s="15">
-        <v>-13.461538461538</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="G17" s="14">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H17" s="15">
-        <v>-4.469273743016</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I17" s="14">
-        <v>441</v>
+        <v>482</v>
       </c>
       <c r="J17" s="14">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="K17" s="15">
-        <v>8.353808353808</v>
+        <v>8.071748878923</v>
       </c>
       <c r="L17" s="15">
-        <v>7.038834951456</v>
+        <v>5.470459518599</v>
       </c>
       <c r="M17" s="15">
-        <v>86.864406779661</v>
+        <v>80.524344569288</v>
       </c>
       <c r="N17" s="15">
-        <v>-26.5</v>
+        <v>-27.844311377245</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D18" s="14">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E18" s="15">
-        <v>-11.363636363636</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="G18" s="14">
         <v>171</v>
       </c>
       <c r="H18" s="15">
-        <v>-21.052631578947</v>
+        <v>-25.146198830409</v>
       </c>
       <c r="I18" s="14">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="J18" s="14">
-        <v>436</v>
+        <v>478</v>
       </c>
       <c r="K18" s="15">
-        <v>-15.825688073394</v>
+        <v>-16.945606694560</v>
       </c>
       <c r="L18" s="15">
-        <v>-13.033175355450</v>
+        <v>-12.362030905077</v>
       </c>
       <c r="M18" s="15">
-        <v>-19.162995594713</v>
+        <v>-18.813905930470</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.701959149645</v>
+        <v>-84.754224270353</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="D19" s="14">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="E19" s="15">
-        <v>-7.567567567567</v>
+        <v>-4.784688995215</v>
       </c>
       <c r="F19" s="14">
-        <v>647</v>
+        <v>678</v>
       </c>
       <c r="G19" s="14">
-        <v>754</v>
+        <v>806</v>
       </c>
       <c r="H19" s="15">
-        <v>-14.190981432360</v>
+        <v>-15.880893300248</v>
       </c>
       <c r="I19" s="14">
-        <v>1808</v>
+        <v>2011</v>
       </c>
       <c r="J19" s="14">
-        <v>1984</v>
+        <v>2193</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.870967741935</v>
+        <v>-8.299133606931</v>
       </c>
       <c r="L19" s="15">
-        <v>-14.027579648121</v>
+        <v>-12.183406113537</v>
       </c>
       <c r="M19" s="15">
-        <v>-9.191361125062</v>
+        <v>-9.004524886877</v>
       </c>
       <c r="N19" s="15">
-        <v>-70.524942940984</v>
+        <v>-70.087758441172</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="F20" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G20" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H20" s="15">
-        <v>5.263157894736</v>
+        <v>38.888888888888</v>
       </c>
       <c r="I20" s="14">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J20" s="14">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K20" s="15">
-        <v>-16.981132075471</v>
+        <v>-7.017543859649</v>
       </c>
       <c r="L20" s="15">
-        <v>-45</v>
+        <v>-40.449438202247</v>
       </c>
       <c r="M20" s="15">
-        <v>-24.137931034482</v>
+        <v>-19.696969696969</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.538158929976</v>
+        <v>-96.159420289855</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D21" s="17">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="E21" s="18">
-        <v>-9.404388714733</v>
+        <v>-12.835820895522</v>
       </c>
       <c r="F21" s="17">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="G21" s="17">
-        <v>1254</v>
+        <v>1308</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.151515151515</v>
+        <v>-18.272171253822</v>
       </c>
       <c r="I21" s="17">
-        <v>2915</v>
+        <v>3213</v>
       </c>
       <c r="J21" s="17">
-        <v>3201</v>
+        <v>3537</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.934707903780</v>
+        <v>-9.160305343511</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.828947368421</v>
+        <v>-11.900191938579</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.671118530884</v>
+        <v>-2.901178603807</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.627645926876</v>
+        <v>-76.433915211970</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D22" s="14">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E22" s="15">
-        <v>-33.333333333333</v>
+        <v>-62.5</v>
       </c>
       <c r="F22" s="14">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G22" s="14">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H22" s="15">
-        <v>-40</v>
+        <v>-56.164383561643</v>
       </c>
       <c r="I22" s="14">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="J22" s="14">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="K22" s="15">
-        <v>-18.300653594771</v>
+        <v>-21.301775147929</v>
       </c>
       <c r="L22" s="15">
-        <v>-8.759124087591</v>
+        <v>-10.135135135135</v>
       </c>
       <c r="M22" s="15">
-        <v>6.837606837606</v>
+        <v>1.526717557251</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D23" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15">
-        <v>18.181818181818</v>
+        <v>57.142857142857</v>
       </c>
       <c r="F23" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G23" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H23" s="15">
-        <v>5.555555555555</v>
+        <v>8.108108108108</v>
       </c>
       <c r="I23" s="14">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="J23" s="14">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K23" s="15">
-        <v>5.494505494505</v>
+        <v>9.183673469387</v>
       </c>
       <c r="L23" s="15">
-        <v>23.076923076923</v>
+        <v>30.487804878048</v>
       </c>
       <c r="M23" s="15">
-        <v>33.333333333333</v>
+        <v>33.75</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="D24" s="14">
-        <v>366</v>
+        <v>437</v>
       </c>
       <c r="E24" s="15">
-        <v>-10.382513661202</v>
+        <v>-26.544622425629</v>
       </c>
       <c r="F24" s="14">
-        <v>1293</v>
+        <v>1266</v>
       </c>
       <c r="G24" s="14">
-        <v>1441</v>
+        <v>1487</v>
       </c>
       <c r="H24" s="15">
-        <v>-10.270645385149</v>
+        <v>-14.862138533961</v>
       </c>
       <c r="I24" s="14">
-        <v>3629</v>
+        <v>3944</v>
       </c>
       <c r="J24" s="14">
-        <v>3913</v>
+        <v>4350</v>
       </c>
       <c r="K24" s="15">
-        <v>-7.257858420649</v>
+        <v>-9.333333333333</v>
       </c>
       <c r="L24" s="15">
-        <v>-15.545729578775</v>
+        <v>-16.705385427666</v>
       </c>
       <c r="M24" s="15">
-        <v>20.205366015236</v>
+        <v>18.616541353383</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>240</v>
       </c>
       <c r="D25" s="14">
-        <v>303</v>
+        <v>359</v>
       </c>
       <c r="E25" s="15">
-        <v>-20.792079207920</v>
+        <v>-33.147632311977</v>
       </c>
       <c r="F25" s="14">
-        <v>1002</v>
+        <v>974</v>
       </c>
       <c r="G25" s="14">
-        <v>1216</v>
+        <v>1242</v>
       </c>
       <c r="H25" s="15">
-        <v>-17.598684210526</v>
+        <v>-21.578099838969</v>
       </c>
       <c r="I25" s="14">
-        <v>2903</v>
+        <v>3144</v>
       </c>
       <c r="J25" s="14">
-        <v>3244</v>
+        <v>3603</v>
       </c>
       <c r="K25" s="15">
-        <v>-10.511713933415</v>
+        <v>-12.739383846794</v>
       </c>
       <c r="L25" s="15">
-        <v>-20.899182561307</v>
+        <v>-22.542498152254</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D26" s="14">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="E26" s="15">
-        <v>7.608695652173</v>
+        <v>-8.474576271186</v>
       </c>
       <c r="F26" s="14">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="G26" s="14">
-        <v>356</v>
+        <v>403</v>
       </c>
       <c r="H26" s="15">
-        <v>3.370786516853</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="I26" s="14">
-        <v>916</v>
+        <v>1022</v>
       </c>
       <c r="J26" s="14">
-        <v>900</v>
+        <v>1017</v>
       </c>
       <c r="K26" s="15">
-        <v>1.777777777777</v>
+        <v>0.491642084562</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.184100418410</v>
+        <v>-1.919385796545</v>
       </c>
       <c r="M26" s="15">
-        <v>33.527696793002</v>
+        <v>36.631016042780</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E27" s="15">
-        <v>-50</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F27" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G27" s="14">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H27" s="15">
-        <v>-25</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I27" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J27" s="14">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="K27" s="15">
-        <v>-13.636363636363</v>
+        <v>-23.636363636363</v>
       </c>
       <c r="L27" s="15">
-        <v>-20.833333333333</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D28" s="14">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F28" s="14">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G28" s="14">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="H28" s="15">
-        <v>-35.714285714285</v>
+        <v>1.587301587301</v>
       </c>
       <c r="I28" s="14">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="J28" s="14">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="K28" s="15">
-        <v>-15.882352941176</v>
+        <v>-6.25</v>
       </c>
       <c r="L28" s="15">
-        <v>-7.741935483870</v>
+        <v>-6.779661016949</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1479,7 +1479,7 @@
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1494,13 +1494,13 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-80</v>
+        <v>-87.5</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.969696969697</v>
+        <v>-97.368421052631</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1520,7 +1520,7 @@
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1535,13 +1535,13 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.296296296296</v>
+        <v>-96.875</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1552,31 +1552,31 @@
         <v>1</v>
       </c>
       <c r="D31" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E31" s="15">
-        <v>0</v>
+        <v>-87.5</v>
       </c>
       <c r="F31" s="14">
         <v>8</v>
       </c>
       <c r="G31" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H31" s="15">
-        <v>-11.111111111111</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="I31" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J31" s="14">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K31" s="15">
-        <v>4.545454545454</v>
+        <v>-10</v>
       </c>
       <c r="L31" s="15">
-        <v>4.545454545454</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbms.xlsx
+++ b/data/source/weekly/cs-en-us-pbms.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>0</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
@@ -896,10 +896,10 @@
         <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>-80</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F15" s="14">
         <v>9</v>
@@ -911,22 +911,22 @@
         <v>-52.631578947368</v>
       </c>
       <c r="I15" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J15" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K15" s="15">
-        <v>-30.434782608695</v>
+        <v>-30.612244897959</v>
       </c>
       <c r="L15" s="15">
-        <v>-11.111111111111</v>
+        <v>-8.108108108108</v>
       </c>
       <c r="M15" s="15">
-        <v>88.235294117647</v>
+        <v>70</v>
       </c>
       <c r="N15" s="15">
-        <v>-30.434782608695</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D16" s="14">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E16" s="15">
-        <v>-53.125</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="F16" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G16" s="14">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="H16" s="15">
-        <v>-41.880341880341</v>
+        <v>-28.155339805825</v>
       </c>
       <c r="I16" s="14">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="J16" s="14">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="K16" s="15">
-        <v>-24.840764331210</v>
+        <v>-23.145400593471</v>
       </c>
       <c r="L16" s="15">
-        <v>-25.316455696202</v>
+        <v>-24.927536231884</v>
       </c>
       <c r="M16" s="15">
-        <v>-7.450980392156</v>
+        <v>-6.834532374100</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.199084668192</v>
+        <v>-89.293096320793</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D17" s="14">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-7.843137254901</v>
       </c>
       <c r="F17" s="14">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="G17" s="14">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H17" s="15">
-        <v>-9.090909090909</v>
+        <v>-3.888888888888</v>
       </c>
       <c r="I17" s="14">
-        <v>482</v>
+        <v>533</v>
       </c>
       <c r="J17" s="14">
-        <v>446</v>
+        <v>497</v>
       </c>
       <c r="K17" s="15">
-        <v>8.071748878923</v>
+        <v>7.243460764587</v>
       </c>
       <c r="L17" s="15">
-        <v>5.470459518599</v>
+        <v>7.243460764587</v>
       </c>
       <c r="M17" s="15">
-        <v>80.524344569288</v>
+        <v>81.292517006802</v>
       </c>
       <c r="N17" s="15">
-        <v>-27.844311377245</v>
+        <v>-27.482993197278</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D18" s="14">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="F18" s="14">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G18" s="14">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H18" s="15">
-        <v>-25.146198830409</v>
+        <v>-28.915662650602</v>
       </c>
       <c r="I18" s="14">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="J18" s="14">
-        <v>478</v>
+        <v>511</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.945606694560</v>
+        <v>-17.221135029354</v>
       </c>
       <c r="L18" s="15">
-        <v>-12.362030905077</v>
+        <v>-11.691022964509</v>
       </c>
       <c r="M18" s="15">
-        <v>-18.813905930470</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.754224270353</v>
+        <v>-85.194259712985</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="D19" s="14">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="E19" s="15">
-        <v>-4.784688995215</v>
+        <v>-2.105263157894</v>
       </c>
       <c r="F19" s="14">
-        <v>678</v>
+        <v>709</v>
       </c>
       <c r="G19" s="14">
-        <v>806</v>
+        <v>797</v>
       </c>
       <c r="H19" s="15">
-        <v>-15.880893300248</v>
+        <v>-11.041405269761</v>
       </c>
       <c r="I19" s="14">
-        <v>2011</v>
+        <v>2195</v>
       </c>
       <c r="J19" s="14">
-        <v>2193</v>
+        <v>2383</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.299133606931</v>
+        <v>-7.889215274863</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.183406113537</v>
+        <v>-10.224948875255</v>
       </c>
       <c r="M19" s="15">
-        <v>-9.004524886877</v>
+        <v>-8.845514950166</v>
       </c>
       <c r="N19" s="15">
-        <v>-70.087758441172</v>
+        <v>-70.245357191270</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>150</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H20" s="15">
-        <v>38.888888888888</v>
+        <v>4.545454545454</v>
       </c>
       <c r="I20" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J20" s="14">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="K20" s="15">
-        <v>-7.017543859649</v>
+        <v>-13.846153846153</v>
       </c>
       <c r="L20" s="15">
-        <v>-40.449438202247</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>-19.696969696969</v>
+        <v>-21.126760563380</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.159420289855</v>
+        <v>-96.251673360107</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D21" s="17">
-        <v>335</v>
+        <v>308</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.835820895522</v>
+        <v>-7.467532467532</v>
       </c>
       <c r="F21" s="17">
-        <v>1069</v>
+        <v>1107</v>
       </c>
       <c r="G21" s="17">
-        <v>1308</v>
+        <v>1287</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.272171253822</v>
+        <v>-13.986013986014</v>
       </c>
       <c r="I21" s="17">
-        <v>3213</v>
+        <v>3502</v>
       </c>
       <c r="J21" s="17">
-        <v>3537</v>
+        <v>3845</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.160305343511</v>
+        <v>-8.920676202860</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.900191938579</v>
+        <v>-10.320102432778</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.901178603807</v>
+        <v>-2.532702477038</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.433915211970</v>
+        <v>-76.592473765122</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D22" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E22" s="15">
-        <v>-62.5</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F22" s="14">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G22" s="14">
         <v>73</v>
       </c>
       <c r="H22" s="15">
-        <v>-56.164383561643</v>
+        <v>-42.465753424657</v>
       </c>
       <c r="I22" s="14">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="J22" s="14">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="K22" s="15">
-        <v>-21.301775147929</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="L22" s="15">
-        <v>-10.135135135135</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="M22" s="15">
-        <v>1.526717557251</v>
+        <v>7.142857142857</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E23" s="15">
-        <v>57.142857142857</v>
+        <v>-30</v>
       </c>
       <c r="F23" s="14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G23" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H23" s="15">
-        <v>8.108108108108</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="J23" s="14">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="K23" s="15">
-        <v>9.183673469387</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L23" s="15">
-        <v>30.487804878048</v>
+        <v>29.545454545454</v>
       </c>
       <c r="M23" s="15">
-        <v>33.75</v>
+        <v>34.117647058823</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="D24" s="14">
-        <v>437</v>
+        <v>399</v>
       </c>
       <c r="E24" s="15">
-        <v>-26.544622425629</v>
+        <v>-12.030075187969</v>
       </c>
       <c r="F24" s="14">
-        <v>1266</v>
+        <v>1325</v>
       </c>
       <c r="G24" s="14">
-        <v>1487</v>
+        <v>1541</v>
       </c>
       <c r="H24" s="15">
-        <v>-14.862138533961</v>
+        <v>-14.016872160934</v>
       </c>
       <c r="I24" s="14">
-        <v>3944</v>
+        <v>4296</v>
       </c>
       <c r="J24" s="14">
-        <v>4350</v>
+        <v>4749</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.333333333333</v>
+        <v>-9.538850284270</v>
       </c>
       <c r="L24" s="15">
-        <v>-16.705385427666</v>
+        <v>-16.403969643899</v>
       </c>
       <c r="M24" s="15">
-        <v>18.616541353383</v>
+        <v>17.025333696540</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="D25" s="14">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.147632311977</v>
+        <v>-26.453488372093</v>
       </c>
       <c r="F25" s="14">
-        <v>974</v>
+        <v>1000</v>
       </c>
       <c r="G25" s="14">
-        <v>1242</v>
+        <v>1282</v>
       </c>
       <c r="H25" s="15">
-        <v>-21.578099838969</v>
+        <v>-21.996879875195</v>
       </c>
       <c r="I25" s="14">
-        <v>3144</v>
+        <v>3404</v>
       </c>
       <c r="J25" s="14">
-        <v>3603</v>
+        <v>3947</v>
       </c>
       <c r="K25" s="15">
-        <v>-12.739383846794</v>
+        <v>-13.757284013174</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.542498152254</v>
+        <v>-22.776769509981</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D26" s="14">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E26" s="15">
-        <v>-8.474576271186</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="G26" s="14">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="H26" s="15">
-        <v>-6.451612903225</v>
+        <v>-6.175771971496</v>
       </c>
       <c r="I26" s="14">
-        <v>1022</v>
+        <v>1126</v>
       </c>
       <c r="J26" s="14">
-        <v>1017</v>
+        <v>1124</v>
       </c>
       <c r="K26" s="15">
-        <v>0.491642084562</v>
+        <v>0.177935943060</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.919385796545</v>
+        <v>-1.141352063213</v>
       </c>
       <c r="M26" s="15">
-        <v>36.631016042780</v>
+        <v>35.990338164251</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" s="14">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>-63.636363636363</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H27" s="15">
-        <v>-46.153846153846</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J27" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K27" s="15">
-        <v>-23.636363636363</v>
+        <v>-22.413793103448</v>
       </c>
       <c r="L27" s="15">
-        <v>-19.230769230769</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E28" s="15">
-        <v>250</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="F28" s="14">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G28" s="14">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H28" s="15">
-        <v>1.587301587301</v>
+        <v>20.967741935483</v>
       </c>
       <c r="I28" s="14">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="J28" s="14">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="K28" s="15">
-        <v>-6.25</v>
+        <v>-6.091370558375</v>
       </c>
       <c r="L28" s="15">
-        <v>-6.779661016949</v>
+        <v>-6.091370558375</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
@@ -1494,13 +1494,13 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="M29" s="15">
         <v>-87.5</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.368421052631</v>
+        <v>-97.560975609756</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
@@ -1535,13 +1535,13 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M30" s="15">
         <v>-80</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.875</v>
+        <v>-97.142857142857</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1549,34 +1549,34 @@
         <v>38</v>
       </c>
       <c r="C31" s="14">
+        <v>2</v>
+      </c>
+      <c r="D31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="14">
-        <v>8</v>
-      </c>
       <c r="E31" s="15">
-        <v>-87.5</v>
+        <v>100</v>
       </c>
       <c r="F31" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G31" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H31" s="15">
-        <v>-46.666666666666</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I31" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J31" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K31" s="15">
-        <v>-10</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,26 +1616,26 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
+      <c r="F33" s="14">
+        <v>1</v>
+      </c>
+      <c r="G33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="14">
         <v>4</v>
       </c>
       <c r="K33" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="L33" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbms.xlsx
+++ b/data/source/weekly/cs-en-us-pbms.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="F15" s="14">
         <v>9</v>
       </c>
       <c r="G15" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H15" s="15">
-        <v>-52.631578947368</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I15" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J15" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K15" s="15">
-        <v>-30.612244897959</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="L15" s="15">
-        <v>-8.108108108108</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="M15" s="15">
-        <v>70</v>
+        <v>80.952380952380</v>
       </c>
       <c r="N15" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.909090909090</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E16" s="15">
-        <v>-8.695652173913</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F16" s="14">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G16" s="14">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="H16" s="15">
-        <v>-28.155339805825</v>
+        <v>-34.710743801652</v>
       </c>
       <c r="I16" s="14">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="J16" s="14">
-        <v>337</v>
+        <v>373</v>
       </c>
       <c r="K16" s="15">
-        <v>-23.145400593471</v>
+        <v>-25.201072386059</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.927536231884</v>
+        <v>-26.190476190476</v>
       </c>
       <c r="M16" s="15">
-        <v>-6.834532374100</v>
+        <v>-5.102040816326</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.293096320793</v>
+        <v>-89.298043728423</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>47</v>
       </c>
       <c r="D17" s="14">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E17" s="15">
-        <v>-7.843137254901</v>
+        <v>-26.5625</v>
       </c>
       <c r="F17" s="14">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="G17" s="14">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="H17" s="15">
-        <v>-3.888888888888</v>
+        <v>-11.219512195122</v>
       </c>
       <c r="I17" s="14">
-        <v>533</v>
+        <v>581</v>
       </c>
       <c r="J17" s="14">
-        <v>497</v>
+        <v>561</v>
       </c>
       <c r="K17" s="15">
-        <v>7.243460764587</v>
+        <v>3.565062388591</v>
       </c>
       <c r="L17" s="15">
-        <v>7.243460764587</v>
+        <v>7.393715341959</v>
       </c>
       <c r="M17" s="15">
-        <v>81.292517006802</v>
+        <v>76.060606060606</v>
       </c>
       <c r="N17" s="15">
-        <v>-27.482993197278</v>
+        <v>-27.192982456140</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D18" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E18" s="15">
-        <v>-24.242424242424</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="F18" s="14">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G18" s="14">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="H18" s="15">
-        <v>-28.915662650602</v>
+        <v>-21.656050955414</v>
       </c>
       <c r="I18" s="14">
-        <v>423</v>
+        <v>454</v>
       </c>
       <c r="J18" s="14">
-        <v>511</v>
+        <v>549</v>
       </c>
       <c r="K18" s="15">
-        <v>-17.221135029354</v>
+        <v>-17.304189435337</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.691022964509</v>
+        <v>-12.015503875969</v>
       </c>
       <c r="M18" s="15">
-        <v>-18.181818181818</v>
+        <v>-16.236162361623</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.194259712985</v>
+        <v>-85.307443365695</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D19" s="14">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="E19" s="15">
-        <v>-2.105263157894</v>
+        <v>9.714285714285</v>
       </c>
       <c r="F19" s="14">
-        <v>709</v>
+        <v>742</v>
       </c>
       <c r="G19" s="14">
-        <v>797</v>
+        <v>759</v>
       </c>
       <c r="H19" s="15">
-        <v>-11.041405269761</v>
+        <v>-2.239789196310</v>
       </c>
       <c r="I19" s="14">
-        <v>2195</v>
+        <v>2382</v>
       </c>
       <c r="J19" s="14">
-        <v>2383</v>
+        <v>2558</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.889215274863</v>
+        <v>-6.880375293197</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.224948875255</v>
+        <v>-8.840413318025</v>
       </c>
       <c r="M19" s="15">
-        <v>-8.845514950166</v>
+        <v>-7.025761124121</v>
       </c>
       <c r="N19" s="15">
-        <v>-70.245357191270</v>
+        <v>-70.127915726109</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F20" s="14">
+        <v>28</v>
+      </c>
+      <c r="G20" s="14">
         <v>23</v>
       </c>
-      <c r="G20" s="14">
-        <v>22</v>
-      </c>
       <c r="H20" s="15">
-        <v>4.545454545454</v>
+        <v>21.739130434782</v>
       </c>
       <c r="I20" s="14">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="J20" s="14">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="K20" s="15">
-        <v>-13.846153846153</v>
+        <v>-9.859154929577</v>
       </c>
       <c r="L20" s="15">
-        <v>-41.666666666666</v>
+        <v>-39.047619047619</v>
       </c>
       <c r="M20" s="15">
-        <v>-21.126760563380</v>
+        <v>-20.987654320987</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.251673360107</v>
+        <v>-96.051819864281</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="D21" s="17">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.467532467532</v>
+        <v>-8.641975308641</v>
       </c>
       <c r="F21" s="17">
-        <v>1107</v>
+        <v>1164</v>
       </c>
       <c r="G21" s="17">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.986013986014</v>
+        <v>-9.486780715396</v>
       </c>
       <c r="I21" s="17">
-        <v>3502</v>
+        <v>3800</v>
       </c>
       <c r="J21" s="17">
-        <v>3845</v>
+        <v>4169</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.920676202860</v>
+        <v>-8.851043415687</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.320102432778</v>
+        <v>-9.545346346108</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.532702477038</v>
+        <v>-0.912646675358</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.592473765122</v>
+        <v>-76.504049959809</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>14</v>
       </c>
       <c r="D22" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E22" s="15">
-        <v>-17.647058823529</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G22" s="14">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H22" s="15">
-        <v>-42.465753424657</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I22" s="14">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="J22" s="14">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="K22" s="15">
-        <v>-19.354838709677</v>
+        <v>-18.5</v>
       </c>
       <c r="L22" s="15">
-        <v>-3.225806451612</v>
+        <v>-4.678362573099</v>
       </c>
       <c r="M22" s="15">
-        <v>7.142857142857</v>
+        <v>10.135135135135</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E23" s="15">
-        <v>-30</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F23" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G23" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-4.878048780487</v>
       </c>
       <c r="I23" s="14">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="J23" s="14">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="K23" s="15">
-        <v>5.555555555555</v>
+        <v>0.826446280991</v>
       </c>
       <c r="L23" s="15">
-        <v>29.545454545454</v>
+        <v>27.083333333333</v>
       </c>
       <c r="M23" s="15">
-        <v>34.117647058823</v>
+        <v>31.182795698924</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="D24" s="14">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E24" s="15">
-        <v>-12.030075187969</v>
+        <v>-17.302798982188</v>
       </c>
       <c r="F24" s="14">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="G24" s="14">
-        <v>1541</v>
+        <v>1595</v>
       </c>
       <c r="H24" s="15">
-        <v>-14.016872160934</v>
+        <v>-16.802507836990</v>
       </c>
       <c r="I24" s="14">
-        <v>4296</v>
+        <v>4621</v>
       </c>
       <c r="J24" s="14">
-        <v>4749</v>
+        <v>5142</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.538850284270</v>
+        <v>-10.132244262932</v>
       </c>
       <c r="L24" s="15">
-        <v>-16.403969643899</v>
+        <v>-15.567330531701</v>
       </c>
       <c r="M24" s="15">
-        <v>17.025333696540</v>
+        <v>16.339375629405</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D25" s="14">
-        <v>344</v>
+        <v>294</v>
       </c>
       <c r="E25" s="15">
-        <v>-26.453488372093</v>
+        <v>-16.326530612244</v>
       </c>
       <c r="F25" s="14">
-        <v>1000</v>
+        <v>989</v>
       </c>
       <c r="G25" s="14">
-        <v>1282</v>
+        <v>1300</v>
       </c>
       <c r="H25" s="15">
-        <v>-21.996879875195</v>
+        <v>-23.923076923076</v>
       </c>
       <c r="I25" s="14">
-        <v>3404</v>
+        <v>3651</v>
       </c>
       <c r="J25" s="14">
-        <v>3947</v>
+        <v>4241</v>
       </c>
       <c r="K25" s="15">
-        <v>-13.757284013174</v>
+        <v>-13.911813251591</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.776769509981</v>
+        <v>-22.252981260647</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D26" s="14">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>6.451612903225</v>
       </c>
       <c r="F26" s="14">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="G26" s="14">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="H26" s="15">
-        <v>-6.175771971496</v>
+        <v>0.487804878048</v>
       </c>
       <c r="I26" s="14">
-        <v>1126</v>
+        <v>1227</v>
       </c>
       <c r="J26" s="14">
-        <v>1124</v>
+        <v>1217</v>
       </c>
       <c r="K26" s="15">
-        <v>0.177935943060</v>
+        <v>0.821692686935</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.141352063213</v>
+        <v>-0.243902439024</v>
       </c>
       <c r="M26" s="15">
-        <v>35.990338164251</v>
+        <v>36.031042128603</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>3</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="F27" s="14">
         <v>13</v>
       </c>
       <c r="G27" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H27" s="15">
-        <v>-45.833333333333</v>
+        <v>-48</v>
       </c>
       <c r="I27" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J27" s="14">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K27" s="15">
-        <v>-22.413793103448</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L27" s="15">
-        <v>-18.181818181818</v>
+        <v>-20.967741935483</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D28" s="14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E28" s="15">
-        <v>-4.761904761904</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G28" s="14">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H28" s="15">
-        <v>20.967741935483</v>
+        <v>25.862068965517</v>
       </c>
       <c r="I28" s="14">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="J28" s="14">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="K28" s="15">
-        <v>-6.091370558375</v>
+        <v>-5.188679245283</v>
       </c>
       <c r="L28" s="15">
-        <v>-6.091370558375</v>
+        <v>-7.373271889400</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>-85.714285714285</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="M29" s="15">
-        <v>-87.5</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.560975609756</v>
+        <v>-95.121951219512</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>-83.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="M30" s="15">
-        <v>-80</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N30" s="15">
-        <v>-97.142857142857</v>
+        <v>-94.285714285714</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1549,34 +1549,34 @@
         <v>38</v>
       </c>
       <c r="C31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E31" s="15">
-        <v>100</v>
+        <v>-87.5</v>
       </c>
       <c r="F31" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G31" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H31" s="15">
-        <v>-30.769230769230</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I31" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J31" s="14">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="K31" s="15">
-        <v>-6.451612903225</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>-6.451612903225</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,32 +1607,32 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="14">
         <v>1</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>0</v>
       </c>
       <c r="I33" s="14">
         <v>2</v>
       </c>
       <c r="J33" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K33" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="L33" s="15">
         <v>-50</v>

--- a/data/source/weekly/cs-en-us-pbms.xlsx
+++ b/data/source/weekly/cs-en-us-pbms.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -882,10 +882,10 @@
         <v>-66.666666666666</v>
       </c>
       <c r="M14" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-92.857142857142</v>
+        <v>-93.103448275862</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,37 +896,37 @@
         <v>3</v>
       </c>
       <c r="D15" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-40</v>
+        <v>200</v>
       </c>
       <c r="F15" s="14">
         <v>9</v>
       </c>
       <c r="G15" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H15" s="15">
-        <v>-57.142857142857</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="I15" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J15" s="14">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K15" s="15">
-        <v>-29.629629629629</v>
+        <v>-29.090909090909</v>
       </c>
       <c r="L15" s="15">
-        <v>-9.523809523809</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M15" s="15">
-        <v>80.952380952380</v>
+        <v>77.272727272727</v>
       </c>
       <c r="N15" s="15">
-        <v>-30.909090909090</v>
+        <v>-31.578947368421</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D16" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16" s="15">
-        <v>-44.444444444444</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="F16" s="14">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G16" s="14">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H16" s="15">
-        <v>-34.710743801652</v>
+        <v>-35.15625</v>
       </c>
       <c r="I16" s="14">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="J16" s="14">
-        <v>373</v>
+        <v>410</v>
       </c>
       <c r="K16" s="15">
-        <v>-25.201072386059</v>
+        <v>-25.609756097561</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.190476190476</v>
+        <v>-25.609756097561</v>
       </c>
       <c r="M16" s="15">
-        <v>-5.102040816326</v>
+        <v>-5.279503105590</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.298043728423</v>
+        <v>-89.145907473309</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D17" s="14">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E17" s="15">
-        <v>-26.5625</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F17" s="14">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="G17" s="14">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H17" s="15">
-        <v>-11.219512195122</v>
+        <v>-14.356435643564</v>
       </c>
       <c r="I17" s="14">
-        <v>581</v>
+        <v>620</v>
       </c>
       <c r="J17" s="14">
-        <v>561</v>
+        <v>610</v>
       </c>
       <c r="K17" s="15">
-        <v>3.565062388591</v>
+        <v>1.639344262295</v>
       </c>
       <c r="L17" s="15">
-        <v>7.393715341959</v>
+        <v>8.391608391608</v>
       </c>
       <c r="M17" s="15">
-        <v>76.060606060606</v>
+        <v>79.190751445086</v>
       </c>
       <c r="N17" s="15">
-        <v>-27.192982456140</v>
+        <v>-28.406466512702</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D18" s="14">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18" s="15">
-        <v>-31.578947368421</v>
+        <v>-37.837837837837</v>
       </c>
       <c r="F18" s="14">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="G18" s="14">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="H18" s="15">
-        <v>-21.656050955414</v>
+        <v>-24.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>454</v>
+        <v>487</v>
       </c>
       <c r="J18" s="14">
-        <v>549</v>
+        <v>586</v>
       </c>
       <c r="K18" s="15">
-        <v>-17.304189435337</v>
+        <v>-16.894197952218</v>
       </c>
       <c r="L18" s="15">
-        <v>-12.015503875969</v>
+        <v>-9.479553903345</v>
       </c>
       <c r="M18" s="15">
-        <v>-16.236162361623</v>
+        <v>-14.561403508771</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.307443365695</v>
+        <v>-85.143380109823</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="D19" s="14">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="E19" s="15">
-        <v>9.714285714285</v>
+        <v>10.457516339869</v>
       </c>
       <c r="F19" s="14">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="G19" s="14">
-        <v>759</v>
+        <v>727</v>
       </c>
       <c r="H19" s="15">
-        <v>-2.239789196310</v>
+        <v>0.962861072902</v>
       </c>
       <c r="I19" s="14">
-        <v>2382</v>
+        <v>2543</v>
       </c>
       <c r="J19" s="14">
-        <v>2558</v>
+        <v>2711</v>
       </c>
       <c r="K19" s="15">
-        <v>-6.880375293197</v>
+        <v>-6.196975285872</v>
       </c>
       <c r="L19" s="15">
-        <v>-8.840413318025</v>
+        <v>-8.983536148890</v>
       </c>
       <c r="M19" s="15">
-        <v>-7.025761124121</v>
+        <v>-8.128612716763</v>
       </c>
       <c r="N19" s="15">
-        <v>-70.127915726109</v>
+        <v>-70.218995198501</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="F20" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G20" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H20" s="15">
-        <v>21.739130434782</v>
+        <v>22.727272727272</v>
       </c>
       <c r="I20" s="14">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="J20" s="14">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K20" s="15">
-        <v>-9.859154929577</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-39.047619047619</v>
+        <v>-35.779816513761</v>
       </c>
       <c r="M20" s="15">
-        <v>-20.987654320987</v>
+        <v>-20.454545454545</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.051819864281</v>
+        <v>-95.972382048331</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="D21" s="17">
-        <v>324</v>
+        <v>281</v>
       </c>
       <c r="E21" s="18">
-        <v>-8.641975308641</v>
+        <v>-7.117437722419</v>
       </c>
       <c r="F21" s="17">
-        <v>1164</v>
+        <v>1139</v>
       </c>
       <c r="G21" s="17">
-        <v>1286</v>
+        <v>1248</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.486780715396</v>
+        <v>-8.733974358974</v>
       </c>
       <c r="I21" s="17">
-        <v>3800</v>
+        <v>4066</v>
       </c>
       <c r="J21" s="17">
-        <v>4169</v>
+        <v>4450</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.851043415687</v>
+        <v>-8.629213483146</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.545346346108</v>
+        <v>-9.058376202191</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.912646675358</v>
+        <v>-1.358563803978</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.504049959809</v>
+        <v>-76.520182479644</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>14</v>
       </c>
       <c r="D22" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F22" s="14">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G22" s="14">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H22" s="15">
-        <v>-29.411764705882</v>
+        <v>-26.5625</v>
       </c>
       <c r="I22" s="14">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="J22" s="14">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="K22" s="15">
-        <v>-18.5</v>
+        <v>-18.433179723502</v>
       </c>
       <c r="L22" s="15">
-        <v>-4.678362573099</v>
+        <v>-4.838709677419</v>
       </c>
       <c r="M22" s="15">
-        <v>10.135135135135</v>
+        <v>12.025316455696</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15">
-        <v>-38.461538461538</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G23" s="14">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H23" s="15">
-        <v>-4.878048780487</v>
+        <v>-10.810810810810</v>
       </c>
       <c r="I23" s="14">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="J23" s="14">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="K23" s="15">
-        <v>0.826446280991</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>27.083333333333</v>
+        <v>21.904761904761</v>
       </c>
       <c r="M23" s="15">
-        <v>31.182795698924</v>
+        <v>29.292929292929</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="D24" s="14">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="E24" s="15">
-        <v>-17.302798982188</v>
+        <v>-9.585492227979</v>
       </c>
       <c r="F24" s="14">
-        <v>1327</v>
+        <v>1352</v>
       </c>
       <c r="G24" s="14">
-        <v>1595</v>
+        <v>1615</v>
       </c>
       <c r="H24" s="15">
-        <v>-16.802507836990</v>
+        <v>-16.284829721362</v>
       </c>
       <c r="I24" s="14">
-        <v>4621</v>
+        <v>4968</v>
       </c>
       <c r="J24" s="14">
-        <v>5142</v>
+        <v>5528</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.132244262932</v>
+        <v>-10.130246020260</v>
       </c>
       <c r="L24" s="15">
-        <v>-15.567330531701</v>
+        <v>-15.567641060503</v>
       </c>
       <c r="M24" s="15">
-        <v>16.339375629405</v>
+        <v>15</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="D25" s="14">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E25" s="15">
-        <v>-16.326530612244</v>
+        <v>-11.724137931034</v>
       </c>
       <c r="F25" s="14">
-        <v>989</v>
+        <v>1004</v>
       </c>
       <c r="G25" s="14">
-        <v>1300</v>
+        <v>1287</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.923076923076</v>
+        <v>-21.989121989122</v>
       </c>
       <c r="I25" s="14">
-        <v>3651</v>
+        <v>3907</v>
       </c>
       <c r="J25" s="14">
-        <v>4241</v>
+        <v>4531</v>
       </c>
       <c r="K25" s="15">
-        <v>-13.911813251591</v>
+        <v>-13.771794305892</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.252981260647</v>
+        <v>-22.310598528534</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D26" s="14">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E26" s="15">
-        <v>6.451612903225</v>
+        <v>6.741573033707</v>
       </c>
       <c r="F26" s="14">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="G26" s="14">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="H26" s="15">
-        <v>0.487804878048</v>
+        <v>0.491400491400</v>
       </c>
       <c r="I26" s="14">
-        <v>1227</v>
+        <v>1320</v>
       </c>
       <c r="J26" s="14">
-        <v>1217</v>
+        <v>1306</v>
       </c>
       <c r="K26" s="15">
-        <v>0.821692686935</v>
+        <v>1.071975497702</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.243902439024</v>
+        <v>0.075815011372</v>
       </c>
       <c r="M26" s="15">
-        <v>36.031042128603</v>
+        <v>33.198789101917</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>3</v>
       </c>
       <c r="D27" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>-40</v>
+        <v>50</v>
       </c>
       <c r="F27" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G27" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H27" s="15">
-        <v>-48</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I27" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J27" s="14">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K27" s="15">
-        <v>-22.222222222222</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L27" s="15">
-        <v>-20.967741935483</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D28" s="14">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E28" s="15">
-        <v>-6.666666666666</v>
+        <v>-48</v>
       </c>
       <c r="F28" s="14">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G28" s="14">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H28" s="15">
-        <v>25.862068965517</v>
+        <v>2.985074626865</v>
       </c>
       <c r="I28" s="14">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="J28" s="14">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="K28" s="15">
-        <v>-5.188679245283</v>
+        <v>-10.126582278481</v>
       </c>
       <c r="L28" s="15">
-        <v>-7.373271889400</v>
+        <v>-9.361702127659</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1500,15 +1500,15 @@
         <v>-81.818181818181</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.121951219512</v>
+        <v>-95.238095238095</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-71.428571428571</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.285714285714</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1552,31 +1552,31 @@
         <v>1</v>
       </c>
       <c r="D31" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E31" s="15">
-        <v>-87.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F31" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G31" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H31" s="15">
-        <v>-66.666666666666</v>
+        <v>-65</v>
       </c>
       <c r="I31" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J31" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K31" s="15">
-        <v>-33.333333333333</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L31" s="15">
-        <v>-27.777777777777</v>
+        <v>-34.146341463414</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-pbms.xlsx
+++ b/data/source/weekly/cs-en-us-pbms.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E15" s="15">
-        <v>200</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F15" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G15" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H15" s="15">
-        <v>-52.631578947368</v>
+        <v>-18.75</v>
       </c>
       <c r="I15" s="14">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J15" s="14">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K15" s="15">
-        <v>-29.090909090909</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="L15" s="15">
-        <v>-7.142857142857</v>
+        <v>4.545454545454</v>
       </c>
       <c r="M15" s="15">
-        <v>77.272727272727</v>
+        <v>70.370370370370</v>
       </c>
       <c r="N15" s="15">
-        <v>-31.578947368421</v>
+        <v>-24.590163934426</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E16" s="15">
-        <v>-32.432432432432</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="F16" s="14">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G16" s="14">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H16" s="15">
-        <v>-35.15625</v>
+        <v>-30.4</v>
       </c>
       <c r="I16" s="14">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="J16" s="14">
-        <v>410</v>
+        <v>439</v>
       </c>
       <c r="K16" s="15">
-        <v>-25.609756097561</v>
+        <v>-25.968109339407</v>
       </c>
       <c r="L16" s="15">
-        <v>-25.609756097561</v>
+        <v>-26.801801801801</v>
       </c>
       <c r="M16" s="15">
-        <v>-5.279503105590</v>
+        <v>-5.523255813953</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.145907473309</v>
+        <v>-89.082969432314</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D17" s="14">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E17" s="15">
-        <v>-28.571428571428</v>
+        <v>24.444444444444</v>
       </c>
       <c r="F17" s="14">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="G17" s="14">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="H17" s="15">
-        <v>-14.356435643564</v>
+        <v>-11.483253588516</v>
       </c>
       <c r="I17" s="14">
-        <v>620</v>
+        <v>675</v>
       </c>
       <c r="J17" s="14">
-        <v>610</v>
+        <v>655</v>
       </c>
       <c r="K17" s="15">
-        <v>1.639344262295</v>
+        <v>3.053435114503</v>
       </c>
       <c r="L17" s="15">
-        <v>8.391608391608</v>
+        <v>8</v>
       </c>
       <c r="M17" s="15">
-        <v>79.190751445086</v>
+        <v>81.940700808625</v>
       </c>
       <c r="N17" s="15">
-        <v>-28.406466512702</v>
+        <v>-28.495762711864</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D18" s="14">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E18" s="15">
-        <v>-37.837837837837</v>
+        <v>-11.363636363636</v>
       </c>
       <c r="F18" s="14">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="G18" s="14">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H18" s="15">
-        <v>-24.666666666666</v>
+        <v>-19.078947368421</v>
       </c>
       <c r="I18" s="14">
-        <v>487</v>
+        <v>529</v>
       </c>
       <c r="J18" s="14">
-        <v>586</v>
+        <v>630</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.894197952218</v>
+        <v>-16.031746031746</v>
       </c>
       <c r="L18" s="15">
-        <v>-9.479553903345</v>
+        <v>-6.866197183098</v>
       </c>
       <c r="M18" s="15">
-        <v>-14.561403508771</v>
+        <v>-10.641891891891</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.143380109823</v>
+        <v>-84.833715596330</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D19" s="14">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="E19" s="15">
-        <v>10.457516339869</v>
+        <v>-1.104972375690</v>
       </c>
       <c r="F19" s="14">
-        <v>734</v>
+        <v>715</v>
       </c>
       <c r="G19" s="14">
-        <v>727</v>
+        <v>699</v>
       </c>
       <c r="H19" s="15">
-        <v>0.962861072902</v>
+        <v>2.288984263233</v>
       </c>
       <c r="I19" s="14">
-        <v>2543</v>
+        <v>2719</v>
       </c>
       <c r="J19" s="14">
-        <v>2711</v>
+        <v>2892</v>
       </c>
       <c r="K19" s="15">
-        <v>-6.196975285872</v>
+        <v>-5.982019363762</v>
       </c>
       <c r="L19" s="15">
-        <v>-8.983536148890</v>
+        <v>-8.574310692669</v>
       </c>
       <c r="M19" s="15">
-        <v>-8.128612716763</v>
+        <v>-8.296795952782</v>
       </c>
       <c r="N19" s="15">
-        <v>-70.218995198501</v>
+        <v>-70.397387044093</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G20" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H20" s="15">
-        <v>22.727272727272</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J20" s="14">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="K20" s="15">
-        <v>-6.666666666666</v>
+        <v>-6.097560975609</v>
       </c>
       <c r="L20" s="15">
-        <v>-35.779816513761</v>
+        <v>-34.188034188034</v>
       </c>
       <c r="M20" s="15">
-        <v>-20.454545454545</v>
+        <v>-18.085106382978</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.972382048331</v>
+        <v>-95.880149812734</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>261</v>
+        <v>307</v>
       </c>
       <c r="D21" s="17">
-        <v>281</v>
+        <v>313</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.117437722419</v>
+        <v>-1.916932907348</v>
       </c>
       <c r="F21" s="17">
-        <v>1139</v>
+        <v>1148</v>
       </c>
       <c r="G21" s="17">
-        <v>1248</v>
+        <v>1226</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.733974358974</v>
+        <v>-6.362153344208</v>
       </c>
       <c r="I21" s="17">
-        <v>4066</v>
+        <v>4373</v>
       </c>
       <c r="J21" s="17">
-        <v>4450</v>
+        <v>4763</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.629213483146</v>
+        <v>-8.188116733151</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.058376202191</v>
+        <v>-8.476349937212</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.358563803978</v>
+        <v>-0.591043418958</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.520182479644</v>
+        <v>-76.429687921090</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D22" s="14">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E22" s="15">
-        <v>-17.647058823529</v>
+        <v>-25</v>
       </c>
       <c r="F22" s="14">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G22" s="14">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H22" s="15">
-        <v>-26.5625</v>
+        <v>-19.642857142857</v>
       </c>
       <c r="I22" s="14">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J22" s="14">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="K22" s="15">
-        <v>-18.433179723502</v>
+        <v>-19.111111111111</v>
       </c>
       <c r="L22" s="15">
-        <v>-4.838709677419</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>12.025316455696</v>
+        <v>10.303030303030</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
         <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G23" s="14">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H23" s="15">
-        <v>-10.810810810810</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I23" s="14">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="J23" s="14">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K23" s="15">
         <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>21.904761904761</v>
+        <v>18.918918918918</v>
       </c>
       <c r="M23" s="15">
-        <v>29.292929292929</v>
+        <v>24.528301886792</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="D24" s="14">
-        <v>386</v>
+        <v>357</v>
       </c>
       <c r="E24" s="15">
-        <v>-9.585492227979</v>
+        <v>5.042016806722</v>
       </c>
       <c r="F24" s="14">
-        <v>1352</v>
+        <v>1405</v>
       </c>
       <c r="G24" s="14">
-        <v>1615</v>
+        <v>1535</v>
       </c>
       <c r="H24" s="15">
-        <v>-16.284829721362</v>
+        <v>-8.469055374592</v>
       </c>
       <c r="I24" s="14">
-        <v>4968</v>
+        <v>5342</v>
       </c>
       <c r="J24" s="14">
-        <v>5528</v>
+        <v>5885</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.130246020260</v>
+        <v>-9.226847918436</v>
       </c>
       <c r="L24" s="15">
-        <v>-15.567641060503</v>
+        <v>-15.165952040654</v>
       </c>
       <c r="M24" s="15">
-        <v>15</v>
+        <v>14.340753424657</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="D25" s="14">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="E25" s="15">
-        <v>-11.724137931034</v>
+        <v>2.611940298507</v>
       </c>
       <c r="F25" s="14">
-        <v>1004</v>
+        <v>1038</v>
       </c>
       <c r="G25" s="14">
-        <v>1287</v>
+        <v>1196</v>
       </c>
       <c r="H25" s="15">
-        <v>-21.989121989122</v>
+        <v>-13.210702341137</v>
       </c>
       <c r="I25" s="14">
-        <v>3907</v>
+        <v>4183</v>
       </c>
       <c r="J25" s="14">
-        <v>4531</v>
+        <v>4799</v>
       </c>
       <c r="K25" s="15">
-        <v>-13.771794305892</v>
+        <v>-12.836007501562</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.310598528534</v>
+        <v>-22.436491748563</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D26" s="14">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="E26" s="15">
-        <v>6.741573033707</v>
+        <v>1.941747572815</v>
       </c>
       <c r="F26" s="14">
         <v>409</v>
       </c>
       <c r="G26" s="14">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="H26" s="15">
-        <v>0.491400491400</v>
+        <v>4.336734693877</v>
       </c>
       <c r="I26" s="14">
-        <v>1320</v>
+        <v>1426</v>
       </c>
       <c r="J26" s="14">
-        <v>1306</v>
+        <v>1409</v>
       </c>
       <c r="K26" s="15">
-        <v>1.071975497702</v>
+        <v>1.206529453513</v>
       </c>
       <c r="L26" s="15">
-        <v>0.075815011372</v>
+        <v>0.210822206605</v>
       </c>
       <c r="M26" s="15">
-        <v>33.198789101917</v>
+        <v>33.271028037383</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E27" s="15">
-        <v>50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F27" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G27" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H27" s="15">
-        <v>-42.857142857142</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J27" s="14">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K27" s="15">
-        <v>-23.076923076923</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>-23.076923076923</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D28" s="14">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E28" s="15">
-        <v>-48</v>
+        <v>109.090909090909</v>
       </c>
       <c r="F28" s="14">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G28" s="14">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H28" s="15">
-        <v>2.985074626865</v>
+        <v>-1.388888888888</v>
       </c>
       <c r="I28" s="14">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="J28" s="14">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="K28" s="15">
-        <v>-10.126582278481</v>
+        <v>-5.241935483870</v>
       </c>
       <c r="L28" s="15">
-        <v>-9.361702127659</v>
+        <v>-8.914728682170</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J29" s="14">
         <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>-77.777777777777</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M29" s="15">
-        <v>-81.818181818181</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.238095238095</v>
+        <v>-91.304347826087</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>2</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,57 +1526,57 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
         <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-71.428571428571</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.444444444444</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="14">
-        <v>3</v>
-      </c>
       <c r="E31" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G31" s="14">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H31" s="15">
-        <v>-65</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="I31" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J31" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K31" s="15">
-        <v>-35.714285714285</v>
+        <v>-34.883720930232</v>
       </c>
       <c r="L31" s="15">
-        <v>-34.146341463414</v>
+        <v>-37.777777777777</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1617,25 +1617,25 @@
         <v>21</v>
       </c>
       <c r="F33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J33" s="14">
         <v>5</v>
       </c>
       <c r="K33" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="L33" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbms.xlsx
+++ b/data/source/weekly/cs-en-us-pbms.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -199,55 +199,55 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>Petit Larceny</t>
+  </si>
+  <si>
+    <t>Retail Theft</t>
+  </si>
+  <si>
+    <t>Misd. Assault</t>
+  </si>
+  <si>
+    <t>UCR Rape*</t>
+  </si>
+  <si>
+    <t>Other Sex Crimes</t>
+  </si>
+  <si>
+    <t>Shooting Vic.</t>
+  </si>
+  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>Petit Larceny</t>
-  </si>
-  <si>
-    <t>Retail Theft</t>
-  </si>
-  <si>
-    <t>Misd. Assault</t>
-  </si>
-  <si>
-    <t>UCR Rape*</t>
-  </si>
-  <si>
-    <t>Other Sex Crimes</t>
-  </si>
-  <si>
-    <t>Shooting Vic.</t>
   </si>
   <si>
     <t>Shooting Inc.</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -851,251 +851,251 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="C14" s="14">
+        <v>2</v>
+      </c>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>100</v>
+      </c>
+      <c r="F14" s="14">
+        <v>2</v>
+      </c>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>100</v>
       </c>
       <c r="I14" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="15">
+        <v>0</v>
+      </c>
+      <c r="L14" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="L14" s="15">
-        <v>-66.666666666666</v>
-      </c>
       <c r="M14" s="15">
-        <v>-66.666666666666</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N14" s="15">
-        <v>-93.103448275862</v>
+        <v>-87.096774193548</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C15" s="14">
+        <v>3</v>
+      </c>
+      <c r="D15" s="14">
         <v>6</v>
       </c>
-      <c r="D15" s="14">
-        <v>7</v>
-      </c>
       <c r="E15" s="15">
-        <v>-14.285714285714</v>
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
         <v>13</v>
       </c>
       <c r="G15" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H15" s="15">
-        <v>-18.75</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I15" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J15" s="14">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K15" s="15">
-        <v>-25.806451612903</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="L15" s="15">
-        <v>4.545454545454</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>70.370370370370</v>
+        <v>65.517241379310</v>
       </c>
       <c r="N15" s="15">
-        <v>-24.590163934426</v>
+        <v>-23.809523809523</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" s="14">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E16" s="15">
-        <v>-31.034482758620</v>
+        <v>-48.648648648648</v>
       </c>
       <c r="F16" s="14">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G16" s="14">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="H16" s="15">
-        <v>-30.4</v>
+        <v>-40.287769784172</v>
       </c>
       <c r="I16" s="14">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="J16" s="14">
-        <v>439</v>
+        <v>476</v>
       </c>
       <c r="K16" s="15">
-        <v>-25.968109339407</v>
+        <v>-27.731092436974</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.801801801801</v>
+        <v>-27.731092436974</v>
       </c>
       <c r="M16" s="15">
-        <v>-5.523255813953</v>
+        <v>-5.234159779614</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.082969432314</v>
+        <v>-89.058524173028</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D17" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E17" s="15">
-        <v>24.444444444444</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G17" s="14">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H17" s="15">
-        <v>-11.483253588516</v>
+        <v>-12.135922330097</v>
       </c>
       <c r="I17" s="14">
-        <v>675</v>
+        <v>723</v>
       </c>
       <c r="J17" s="14">
-        <v>655</v>
+        <v>703</v>
       </c>
       <c r="K17" s="15">
-        <v>3.053435114503</v>
+        <v>2.844950213371</v>
       </c>
       <c r="L17" s="15">
-        <v>8</v>
+        <v>6.952662721893</v>
       </c>
       <c r="M17" s="15">
-        <v>81.940700808625</v>
+        <v>84.438775510204</v>
       </c>
       <c r="N17" s="15">
-        <v>-28.495762711864</v>
+        <v>-28.557312252964</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D18" s="14">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E18" s="15">
-        <v>-11.363636363636</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="F18" s="14">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G18" s="14">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H18" s="15">
-        <v>-19.078947368421</v>
+        <v>-19.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>529</v>
+        <v>555</v>
       </c>
       <c r="J18" s="14">
-        <v>630</v>
+        <v>661</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.031746031746</v>
+        <v>-16.036308623298</v>
       </c>
       <c r="L18" s="15">
-        <v>-6.866197183098</v>
+        <v>-10.048622366288</v>
       </c>
       <c r="M18" s="15">
-        <v>-10.641891891891</v>
+        <v>-10.048622366288</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.833715596330</v>
+        <v>-85.048491379310</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D19" s="14">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="E19" s="15">
-        <v>-1.104972375690</v>
+        <v>0.591715976331</v>
       </c>
       <c r="F19" s="14">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="G19" s="14">
-        <v>699</v>
+        <v>678</v>
       </c>
       <c r="H19" s="15">
-        <v>2.288984263233</v>
+        <v>3.244837758112</v>
       </c>
       <c r="I19" s="14">
-        <v>2719</v>
+        <v>2885</v>
       </c>
       <c r="J19" s="14">
-        <v>2892</v>
+        <v>3061</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.982019363762</v>
+        <v>-5.749754982032</v>
       </c>
       <c r="L19" s="15">
-        <v>-8.574310692669</v>
+        <v>-8.702531645569</v>
       </c>
       <c r="M19" s="15">
-        <v>-8.296795952782</v>
+        <v>-9.105229993698</v>
       </c>
       <c r="N19" s="15">
-        <v>-70.397387044093</v>
+        <v>-70.573235414116</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C20" s="14">
         <v>7</v>
@@ -1107,400 +1107,400 @@
         <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G20" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J20" s="14">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K20" s="15">
-        <v>-6.097560975609</v>
+        <v>-5.617977528089</v>
       </c>
       <c r="L20" s="15">
-        <v>-34.188034188034</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-18.085106382978</v>
+        <v>-21.495327102803</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.880149812734</v>
+        <v>-95.761856710393</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>307</v>
+        <v>270</v>
       </c>
       <c r="D21" s="17">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="E21" s="18">
-        <v>-1.916932907348</v>
+        <v>-9.698996655518</v>
       </c>
       <c r="F21" s="17">
-        <v>1148</v>
+        <v>1128</v>
       </c>
       <c r="G21" s="17">
-        <v>1226</v>
+        <v>1217</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.362153344208</v>
+        <v>-7.313064913722</v>
       </c>
       <c r="I21" s="17">
-        <v>4373</v>
+        <v>4643</v>
       </c>
       <c r="J21" s="17">
-        <v>4763</v>
+        <v>5062</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.188116733151</v>
+        <v>-8.277360726985</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.476349937212</v>
+        <v>-9.067763415589</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.591043418958</v>
+        <v>-0.981019407123</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.429687921090</v>
+        <v>-76.488758355276</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C22" s="14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22" s="15">
-        <v>-25</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F22" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G22" s="14">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="H22" s="15">
-        <v>-19.642857142857</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="I22" s="14">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="J22" s="14">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="K22" s="15">
-        <v>-19.111111111111</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>-6.666666666666</v>
+        <v>-3.465346534653</v>
       </c>
       <c r="M22" s="15">
-        <v>10.303030303030</v>
+        <v>12.716763005780</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F23" s="14">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G23" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H23" s="15">
-        <v>-23.529411764705</v>
+        <v>6.25</v>
       </c>
       <c r="I23" s="14">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="J23" s="14">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>4.285714285714</v>
       </c>
       <c r="L23" s="15">
-        <v>18.918918918918</v>
+        <v>19.672131147541</v>
       </c>
       <c r="M23" s="15">
-        <v>24.528301886792</v>
+        <v>26.956521739130</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="D24" s="14">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="E24" s="15">
-        <v>5.042016806722</v>
+        <v>-3.713527851458</v>
       </c>
       <c r="F24" s="14">
-        <v>1405</v>
+        <v>1416</v>
       </c>
       <c r="G24" s="14">
-        <v>1535</v>
+        <v>1513</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.469055374592</v>
+        <v>-6.411103767349</v>
       </c>
       <c r="I24" s="14">
-        <v>5342</v>
+        <v>5706</v>
       </c>
       <c r="J24" s="14">
-        <v>5885</v>
+        <v>6262</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.226847918436</v>
+        <v>-8.878952411370</v>
       </c>
       <c r="L24" s="15">
-        <v>-15.165952040654</v>
+        <v>-15.316117542297</v>
       </c>
       <c r="M24" s="15">
-        <v>14.340753424657</v>
+        <v>14.532316338819</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D25" s="14">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="E25" s="15">
-        <v>2.611940298507</v>
+        <v>-4.878048780487</v>
       </c>
       <c r="F25" s="14">
-        <v>1038</v>
+        <v>1058</v>
       </c>
       <c r="G25" s="14">
-        <v>1196</v>
+        <v>1139</v>
       </c>
       <c r="H25" s="15">
-        <v>-13.210702341137</v>
+        <v>-7.111501316944</v>
       </c>
       <c r="I25" s="14">
-        <v>4183</v>
+        <v>4458</v>
       </c>
       <c r="J25" s="14">
-        <v>4799</v>
+        <v>5086</v>
       </c>
       <c r="K25" s="15">
-        <v>-12.836007501562</v>
+        <v>-12.347620920173</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.436491748563</v>
+        <v>-22.885313959522</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D26" s="14">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E26" s="15">
-        <v>1.941747572815</v>
+        <v>17.708333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="G26" s="14">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="H26" s="15">
-        <v>4.336734693877</v>
+        <v>8.923884514435</v>
       </c>
       <c r="I26" s="14">
-        <v>1426</v>
+        <v>1537</v>
       </c>
       <c r="J26" s="14">
-        <v>1409</v>
+        <v>1505</v>
       </c>
       <c r="K26" s="15">
-        <v>1.206529453513</v>
+        <v>2.126245847176</v>
       </c>
       <c r="L26" s="15">
-        <v>0.210822206605</v>
+        <v>0.919238345370</v>
       </c>
       <c r="M26" s="15">
-        <v>33.271028037383</v>
+        <v>33.768494342906</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D27" s="14">
         <v>7</v>
       </c>
       <c r="E27" s="15">
-        <v>28.571428571428</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F27" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G27" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I27" s="14">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J27" s="14">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="K27" s="15">
-        <v>-16.666666666666</v>
+        <v>-21.518987341772</v>
       </c>
       <c r="L27" s="15">
-        <v>-14.285714285714</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D28" s="14">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E28" s="15">
-        <v>109.090909090909</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="F28" s="14">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G28" s="14">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H28" s="15">
-        <v>-1.388888888888</v>
+        <v>-14.102564102564</v>
       </c>
       <c r="I28" s="14">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="J28" s="14">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="K28" s="15">
-        <v>-5.241935483870</v>
+        <v>-8.363636363636</v>
       </c>
       <c r="L28" s="15">
-        <v>-8.914728682170</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="14">
         <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I29" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J29" s="14">
         <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="L29" s="15">
-        <v>-55.555555555555</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-63.636363636363</v>
+        <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.304347826087</v>
+        <v>-88.461538461538</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,54 +1508,54 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="14">
         <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="M30" s="15">
-        <v>-42.857142857142</v>
+        <v>-37.5</v>
       </c>
       <c r="N30" s="15">
-        <v>-90</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="14">
         <v>1</v>
       </c>
       <c r="E31" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F31" s="14">
         <v>5</v>
@@ -1567,22 +1567,22 @@
         <v>-61.538461538461</v>
       </c>
       <c r="I31" s="14">
+        <v>30</v>
+      </c>
+      <c r="J31" s="14">
+        <v>44</v>
+      </c>
+      <c r="K31" s="15">
+        <v>-31.818181818181</v>
+      </c>
+      <c r="L31" s="15">
+        <v>-38.775510204081</v>
+      </c>
+      <c r="M31" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="J31" s="14">
-        <v>43</v>
-      </c>
-      <c r="K31" s="15">
-        <v>-34.883720930232</v>
-      </c>
-      <c r="L31" s="15">
-        <v>-37.777777777777</v>
-      </c>
-      <c r="M31" s="13" t="s">
-        <v>21</v>
-      </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,23 +1607,23 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="14">
         <v>1</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" s="14">
-        <v>2</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I33" s="14">
         <v>3</v>
@@ -1638,10 +1638,10 @@
         <v>-25</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>207</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C41" s="14">
         <v>14866</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C42" s="14">
         <v>3997</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C43" s="14">
         <v>16090</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C44" s="14">
         <v>44811</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C45" s="14">
         <v>9446</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C46" s="17">
         <v>89541</v>

--- a/data/source/weekly/cs-en-us-pbms.xlsx
+++ b/data/source/weekly/cs-en-us-pbms.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -199,6 +199,12 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -223,9 +229,6 @@
     <t>Transit</t>
   </si>
   <si>
-    <t>***.*</t>
-  </si>
-  <si>
     <t>Housing</t>
   </si>
   <si>
@@ -245,9 +248,6 @@
   </si>
   <si>
     <t>Shooting Vic.</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Shooting Inc.</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -851,14 +851,14 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>2</v>
-      </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>100</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>2</v>
@@ -885,622 +885,622 @@
         <v>-42.857142857142</v>
       </c>
       <c r="N14" s="15">
-        <v>-87.096774193548</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" s="14">
         <v>6</v>
       </c>
       <c r="E15" s="15">
-        <v>-50</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F15" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G15" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H15" s="15">
-        <v>-31.578947368421</v>
+        <v>-20</v>
       </c>
       <c r="I15" s="14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J15" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K15" s="15">
-        <v>-29.411764705882</v>
+        <v>-28.378378378378</v>
       </c>
       <c r="L15" s="15">
-        <v>6.666666666666</v>
+        <v>12.765957446808</v>
       </c>
       <c r="M15" s="15">
-        <v>65.517241379310</v>
+        <v>65.625</v>
       </c>
       <c r="N15" s="15">
-        <v>-23.809523809523</v>
+        <v>-19.696969696969</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D16" s="14">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E16" s="15">
-        <v>-48.648648648648</v>
+        <v>-28.888888888888</v>
       </c>
       <c r="F16" s="14">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G16" s="14">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="H16" s="15">
-        <v>-40.287769784172</v>
+        <v>-36.486486486486</v>
       </c>
       <c r="I16" s="14">
-        <v>344</v>
+        <v>377</v>
       </c>
       <c r="J16" s="14">
-        <v>476</v>
+        <v>521</v>
       </c>
       <c r="K16" s="15">
-        <v>-27.731092436974</v>
+        <v>-27.639155470249</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.731092436974</v>
+        <v>-26.3671875</v>
       </c>
       <c r="M16" s="15">
-        <v>-5.234159779614</v>
+        <v>-1.822916666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.058524173028</v>
+        <v>-88.641156974992</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="14">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="E17" s="15">
-        <v>-4.166666666666</v>
+        <v>-33.802816901408</v>
       </c>
       <c r="F17" s="14">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G17" s="14">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="H17" s="15">
-        <v>-12.135922330097</v>
+        <v>-15.492957746478</v>
       </c>
       <c r="I17" s="14">
-        <v>723</v>
+        <v>773</v>
       </c>
       <c r="J17" s="14">
-        <v>703</v>
+        <v>774</v>
       </c>
       <c r="K17" s="15">
-        <v>2.844950213371</v>
+        <v>-0.129198966408</v>
       </c>
       <c r="L17" s="15">
-        <v>6.952662721893</v>
+        <v>5.601092896174</v>
       </c>
       <c r="M17" s="15">
-        <v>84.438775510204</v>
+        <v>84.486873508353</v>
       </c>
       <c r="N17" s="15">
-        <v>-28.557312252964</v>
+        <v>-28.293135435992</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D18" s="14">
         <v>31</v>
       </c>
       <c r="E18" s="15">
-        <v>-25.806451612903</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="F18" s="14">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G18" s="14">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H18" s="15">
-        <v>-19.333333333333</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I18" s="14">
-        <v>555</v>
+        <v>586</v>
       </c>
       <c r="J18" s="14">
-        <v>661</v>
+        <v>692</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.036308623298</v>
+        <v>-15.317919075144</v>
       </c>
       <c r="L18" s="15">
-        <v>-10.048622366288</v>
+        <v>-11.077389984825</v>
       </c>
       <c r="M18" s="15">
-        <v>-10.048622366288</v>
+        <v>-8.580343213728</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.048491379310</v>
+        <v>-85.054832950777</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D19" s="14">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="E19" s="15">
-        <v>0.591715976331</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="F19" s="14">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="G19" s="14">
-        <v>678</v>
+        <v>691</v>
       </c>
       <c r="H19" s="15">
-        <v>3.244837758112</v>
+        <v>0.434153400868</v>
       </c>
       <c r="I19" s="14">
-        <v>2885</v>
+        <v>3069</v>
       </c>
       <c r="J19" s="14">
-        <v>3061</v>
+        <v>3249</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.749754982032</v>
+        <v>-5.540166204986</v>
       </c>
       <c r="L19" s="15">
-        <v>-8.702531645569</v>
+        <v>-8.415398388540</v>
       </c>
       <c r="M19" s="15">
-        <v>-9.105229993698</v>
+        <v>-8.278541542139</v>
       </c>
       <c r="N19" s="15">
-        <v>-70.573235414116</v>
+        <v>-70.456295725837</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
         <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G20" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H20" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="J20" s="14">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K20" s="15">
-        <v>-5.617977528089</v>
+        <v>-7.216494845360</v>
       </c>
       <c r="L20" s="15">
-        <v>-33.333333333333</v>
+        <v>-33.823529411764</v>
       </c>
       <c r="M20" s="15">
-        <v>-21.495327102803</v>
+        <v>-19.642857142857</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.761856710393</v>
+        <v>-95.734597156398</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="D21" s="17">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="E21" s="18">
-        <v>-9.698996655518</v>
+        <v>-14.040114613180</v>
       </c>
       <c r="F21" s="17">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="G21" s="17">
-        <v>1217</v>
+        <v>1242</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.313064913722</v>
+        <v>-9.098228663446</v>
       </c>
       <c r="I21" s="17">
-        <v>4643</v>
+        <v>4952</v>
       </c>
       <c r="J21" s="17">
-        <v>5062</v>
+        <v>5411</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.277360726985</v>
+        <v>-8.482720384402</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.067763415589</v>
+        <v>-9.020760609957</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.981019407123</v>
+        <v>0.222626998583</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.488758355276</v>
+        <v>-76.324344999043</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D22" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E22" s="15">
-        <v>44.444444444444</v>
+        <v>45.454545454545</v>
       </c>
       <c r="F22" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G22" s="14">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H22" s="15">
-        <v>-4.166666666666</v>
+        <v>8.888888888888</v>
       </c>
       <c r="I22" s="14">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="J22" s="14">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="K22" s="15">
-        <v>-16.666666666666</v>
+        <v>-13.061224489795</v>
       </c>
       <c r="L22" s="15">
-        <v>-3.465346534653</v>
+        <v>-1.388888888888</v>
       </c>
       <c r="M22" s="15">
-        <v>12.716763005780</v>
+        <v>15.760869565217</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D23" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E23" s="15">
-        <v>75</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F23" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G23" s="14">
         <v>32</v>
       </c>
       <c r="H23" s="15">
-        <v>6.25</v>
+        <v>12.5</v>
       </c>
       <c r="I23" s="14">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="J23" s="14">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="K23" s="15">
-        <v>4.285714285714</v>
+        <v>2.614379084967</v>
       </c>
       <c r="L23" s="15">
-        <v>19.672131147541</v>
+        <v>19.847328244274</v>
       </c>
       <c r="M23" s="15">
-        <v>26.956521739130</v>
+        <v>30.833333333333</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="D24" s="14">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="E24" s="15">
-        <v>-3.713527851458</v>
+        <v>2.590673575129</v>
       </c>
       <c r="F24" s="14">
-        <v>1416</v>
+        <v>1485</v>
       </c>
       <c r="G24" s="14">
-        <v>1513</v>
+        <v>1506</v>
       </c>
       <c r="H24" s="15">
-        <v>-6.411103767349</v>
+        <v>-1.394422310756</v>
       </c>
       <c r="I24" s="14">
-        <v>5706</v>
+        <v>6097</v>
       </c>
       <c r="J24" s="14">
-        <v>6262</v>
+        <v>6648</v>
       </c>
       <c r="K24" s="15">
-        <v>-8.878952411370</v>
+        <v>-8.288206979542</v>
       </c>
       <c r="L24" s="15">
-        <v>-15.316117542297</v>
+        <v>-14.727272727272</v>
       </c>
       <c r="M24" s="15">
-        <v>14.532316338819</v>
+        <v>15.102888427411</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="D25" s="14">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E25" s="15">
-        <v>-4.878048780487</v>
+        <v>-5.647840531561</v>
       </c>
       <c r="F25" s="14">
-        <v>1058</v>
+        <v>1097</v>
       </c>
       <c r="G25" s="14">
-        <v>1139</v>
+        <v>1146</v>
       </c>
       <c r="H25" s="15">
-        <v>-7.111501316944</v>
+        <v>-4.275741710296</v>
       </c>
       <c r="I25" s="14">
-        <v>4458</v>
+        <v>4743</v>
       </c>
       <c r="J25" s="14">
-        <v>5086</v>
+        <v>5387</v>
       </c>
       <c r="K25" s="15">
-        <v>-12.347620920173</v>
+        <v>-11.954705773157</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.885313959522</v>
+        <v>-22.601174934725</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D26" s="14">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="E26" s="15">
-        <v>17.708333333333</v>
+        <v>-15.596330275229</v>
       </c>
       <c r="F26" s="14">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="G26" s="14">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="H26" s="15">
-        <v>8.923884514435</v>
+        <v>2.518891687657</v>
       </c>
       <c r="I26" s="14">
-        <v>1537</v>
+        <v>1626</v>
       </c>
       <c r="J26" s="14">
-        <v>1505</v>
+        <v>1614</v>
       </c>
       <c r="K26" s="15">
-        <v>2.126245847176</v>
+        <v>0.743494423791</v>
       </c>
       <c r="L26" s="15">
-        <v>0.919238345370</v>
+        <v>1.752190237797</v>
       </c>
       <c r="M26" s="15">
-        <v>33.768494342906</v>
+        <v>34.158415841584</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D27" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" s="15">
-        <v>-57.142857142857</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G27" s="14">
+        <v>22</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-9.090909090909</v>
+      </c>
+      <c r="I27" s="14">
+        <v>67</v>
+      </c>
+      <c r="J27" s="14">
+        <v>85</v>
+      </c>
+      <c r="K27" s="15">
+        <v>-21.176470588235</v>
+      </c>
+      <c r="L27" s="15">
+        <v>-11.842105263157</v>
+      </c>
+      <c r="M27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="15">
-        <v>-23.809523809523</v>
-      </c>
-      <c r="I27" s="14">
-        <v>62</v>
-      </c>
-      <c r="J27" s="14">
-        <v>79</v>
-      </c>
-      <c r="K27" s="15">
-        <v>-21.518987341772</v>
-      </c>
-      <c r="L27" s="15">
-        <v>-13.888888888888</v>
-      </c>
-      <c r="M27" s="13" t="s">
-        <v>28</v>
-      </c>
       <c r="N27" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D28" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E28" s="15">
-        <v>-37.037037037037</v>
+        <v>-16</v>
       </c>
       <c r="F28" s="14">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G28" s="14">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H28" s="15">
-        <v>-14.102564102564</v>
+        <v>-15.909090909090</v>
       </c>
       <c r="I28" s="14">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="J28" s="14">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="K28" s="15">
-        <v>-8.363636363636</v>
+        <v>-9</v>
       </c>
       <c r="L28" s="15">
-        <v>-8.695652173913</v>
+        <v>-5.536332179930</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>2</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>28</v>
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
       </c>
       <c r="F29" s="14">
         <v>5</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>28</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>400</v>
       </c>
       <c r="I29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L29" s="15">
-        <v>-33.333333333333</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M29" s="15">
-        <v>-50</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.461538461538</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,79 +1510,79 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>28</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
         <v>4</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>28</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>300</v>
       </c>
       <c r="I30" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="L30" s="15">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.888888888888</v>
+        <v>-87.755102040816</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>5</v>
       </c>
       <c r="G31" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H31" s="15">
-        <v>-61.538461538461</v>
+        <v>-37.5</v>
       </c>
       <c r="I31" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J31" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K31" s="15">
-        <v>-31.818181818181</v>
+        <v>-34.042553191489</v>
       </c>
       <c r="L31" s="15">
-        <v>-38.775510204081</v>
+        <v>-40.384615384615</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,13 +1608,13 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>28</v>
+        <v>20</v>
+      </c>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1629,19 +1629,19 @@
         <v>3</v>
       </c>
       <c r="J33" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K33" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="L33" s="15">
         <v>-25</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>207</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>14866</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>3997</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>16090</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>44811</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>9446</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>89541</v>

--- a/data/source/weekly/cs-en-us-pbms.xlsx
+++ b/data/source/weekly/cs-en-us-pbms.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -199,67 +199,67 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>Petit Larceny</t>
+  </si>
+  <si>
+    <t>Retail Theft</t>
+  </si>
+  <si>
+    <t>Misd. Assault</t>
+  </si>
+  <si>
+    <t>UCR Rape*</t>
+  </si>
+  <si>
+    <t>Other Sex Crimes</t>
+  </si>
+  <si>
+    <t>Shooting Vic.</t>
+  </si>
+  <si>
+    <t>Shooting Inc.</t>
+  </si>
+  <si>
+    <t>Hate Crimes</t>
+  </si>
+  <si>
+    <t>Traffic Statistics</t>
+  </si>
+  <si>
+    <t>Traffic Fatalities</t>
+  </si>
+  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>Petit Larceny</t>
-  </si>
-  <si>
-    <t>Retail Theft</t>
-  </si>
-  <si>
-    <t>Misd. Assault</t>
-  </si>
-  <si>
-    <t>UCR Rape*</t>
-  </si>
-  <si>
-    <t>Other Sex Crimes</t>
-  </si>
-  <si>
-    <t>Shooting Vic.</t>
-  </si>
-  <si>
-    <t>Shooting Inc.</t>
-  </si>
-  <si>
-    <t>Hate Crimes</t>
-  </si>
-  <si>
-    <t>Traffic Statistics</t>
-  </si>
-  <si>
-    <t>Traffic Fatalities</t>
   </si>
   <si>
     <t>Historical Perspective</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -851,620 +851,620 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="C14" s="14">
+        <v>2</v>
+      </c>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>100</v>
       </c>
       <c r="F14" s="14">
+        <v>4</v>
+      </c>
+      <c r="G14" s="14">
         <v>2</v>
-      </c>
-      <c r="G14" s="14">
-        <v>1</v>
       </c>
       <c r="H14" s="15">
         <v>100</v>
       </c>
       <c r="I14" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K14" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L14" s="15">
-        <v>-33.333333333333</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M14" s="15">
-        <v>-42.857142857142</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N14" s="15">
-        <v>-88.235294117647</v>
+        <v>-82.857142857142</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" s="14">
         <v>6</v>
       </c>
       <c r="E15" s="15">
-        <v>-16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F15" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H15" s="15">
-        <v>-20</v>
+        <v>-32</v>
       </c>
       <c r="I15" s="14">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J15" s="14">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K15" s="15">
-        <v>-28.378378378378</v>
+        <v>-28.75</v>
       </c>
       <c r="L15" s="15">
-        <v>12.765957446808</v>
+        <v>16.326530612244</v>
       </c>
       <c r="M15" s="15">
-        <v>65.625</v>
+        <v>78.125</v>
       </c>
       <c r="N15" s="15">
-        <v>-19.696969696969</v>
+        <v>-14.925373134328</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D16" s="14">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E16" s="15">
-        <v>-28.888888888888</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F16" s="14">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G16" s="14">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H16" s="15">
-        <v>-36.486486486486</v>
+        <v>-36.111111111111</v>
       </c>
       <c r="I16" s="14">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="J16" s="14">
-        <v>521</v>
+        <v>554</v>
       </c>
       <c r="K16" s="15">
-        <v>-27.639155470249</v>
+        <v>-28.158844765343</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.3671875</v>
+        <v>-26.159554730983</v>
       </c>
       <c r="M16" s="15">
-        <v>-1.822916666666</v>
+        <v>-2.450980392156</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.641156974992</v>
+        <v>-88.712422007941</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="D17" s="14">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.802816901408</v>
+        <v>42.222222222222</v>
       </c>
       <c r="F17" s="14">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="G17" s="14">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H17" s="15">
-        <v>-15.492957746478</v>
+        <v>0.478468899521</v>
       </c>
       <c r="I17" s="14">
-        <v>773</v>
+        <v>838</v>
       </c>
       <c r="J17" s="14">
-        <v>774</v>
+        <v>819</v>
       </c>
       <c r="K17" s="15">
-        <v>-0.129198966408</v>
+        <v>2.319902319902</v>
       </c>
       <c r="L17" s="15">
-        <v>5.601092896174</v>
+        <v>7.298335467349</v>
       </c>
       <c r="M17" s="15">
-        <v>84.486873508353</v>
+        <v>87.892376681614</v>
       </c>
       <c r="N17" s="15">
-        <v>-28.293135435992</v>
+        <v>-27.193744569939</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D18" s="14">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E18" s="15">
-        <v>-9.677419354838</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="G18" s="14">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H18" s="15">
-        <v>-18.181818181818</v>
+        <v>-12.162162162162</v>
       </c>
       <c r="I18" s="14">
-        <v>586</v>
+        <v>627</v>
       </c>
       <c r="J18" s="14">
-        <v>692</v>
+        <v>734</v>
       </c>
       <c r="K18" s="15">
-        <v>-15.317919075144</v>
+        <v>-14.577656675749</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.077389984825</v>
+        <v>-10.171919770773</v>
       </c>
       <c r="M18" s="15">
-        <v>-8.580343213728</v>
+        <v>-8.064516129032</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.054832950777</v>
+        <v>-84.836759371221</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D19" s="14">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="E19" s="15">
-        <v>-4.255319148936</v>
+        <v>-10.945273631840</v>
       </c>
       <c r="F19" s="14">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="G19" s="14">
-        <v>691</v>
+        <v>739</v>
       </c>
       <c r="H19" s="15">
-        <v>0.434153400868</v>
+        <v>-5.142083897158</v>
       </c>
       <c r="I19" s="14">
-        <v>3069</v>
+        <v>3251</v>
       </c>
       <c r="J19" s="14">
-        <v>3249</v>
+        <v>3450</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.540166204986</v>
+        <v>-5.768115942028</v>
       </c>
       <c r="L19" s="15">
-        <v>-8.415398388540</v>
+        <v>-8.756665731125</v>
       </c>
       <c r="M19" s="15">
-        <v>-8.278541542139</v>
+        <v>-8.448324415657</v>
       </c>
       <c r="N19" s="15">
-        <v>-70.456295725837</v>
+        <v>-70.402403495994</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F20" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G20" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="I20" s="14">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J20" s="14">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="K20" s="15">
-        <v>-7.216494845360</v>
+        <v>-11.320754716981</v>
       </c>
       <c r="L20" s="15">
-        <v>-33.823529411764</v>
+        <v>-32.857142857142</v>
       </c>
       <c r="M20" s="15">
-        <v>-19.642857142857</v>
+        <v>-23.577235772357</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.734597156398</v>
+        <v>-95.752372345232</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="D21" s="17">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="E21" s="18">
-        <v>-14.040114613180</v>
+        <v>-8.011869436201</v>
       </c>
       <c r="F21" s="17">
-        <v>1129</v>
+        <v>1178</v>
       </c>
       <c r="G21" s="17">
-        <v>1242</v>
+        <v>1298</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.098228663446</v>
+        <v>-9.244992295839</v>
       </c>
       <c r="I21" s="17">
-        <v>4952</v>
+        <v>5271</v>
       </c>
       <c r="J21" s="17">
-        <v>5411</v>
+        <v>5748</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.482720384402</v>
+        <v>-8.298538622129</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.020760609957</v>
+        <v>-8.758871386532</v>
       </c>
       <c r="M21" s="18">
-        <v>0.222626998583</v>
+        <v>0.419127452848</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.324344999043</v>
+        <v>-76.161186739631</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C22" s="14">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D22" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E22" s="15">
-        <v>45.454545454545</v>
+        <v>12.5</v>
       </c>
       <c r="F22" s="14">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G22" s="14">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H22" s="15">
-        <v>8.888888888888</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I22" s="14">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="J22" s="14">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="K22" s="15">
-        <v>-13.061224489795</v>
+        <v>-12.252964426877</v>
       </c>
       <c r="L22" s="15">
-        <v>-1.388888888888</v>
+        <v>-4.721030042918</v>
       </c>
       <c r="M22" s="15">
-        <v>15.760869565217</v>
+        <v>17.460317460317</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D23" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>-7.692307692307</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G23" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H23" s="15">
-        <v>12.5</v>
+        <v>19.354838709677</v>
       </c>
       <c r="I23" s="14">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="J23" s="14">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="K23" s="15">
-        <v>2.614379084967</v>
+        <v>3.773584905660</v>
       </c>
       <c r="L23" s="15">
-        <v>19.847328244274</v>
+        <v>20.437956204379</v>
       </c>
       <c r="M23" s="15">
-        <v>30.833333333333</v>
+        <v>23.134328358209</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>396</v>
+        <v>308</v>
       </c>
       <c r="D24" s="14">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="E24" s="15">
-        <v>2.590673575129</v>
+        <v>-18.733509234828</v>
       </c>
       <c r="F24" s="14">
-        <v>1485</v>
+        <v>1439</v>
       </c>
       <c r="G24" s="14">
-        <v>1506</v>
+        <v>1499</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.394422310756</v>
+        <v>-4.002668445630</v>
       </c>
       <c r="I24" s="14">
-        <v>6097</v>
+        <v>6396</v>
       </c>
       <c r="J24" s="14">
-        <v>6648</v>
+        <v>7027</v>
       </c>
       <c r="K24" s="15">
-        <v>-8.288206979542</v>
+        <v>-8.979649921730</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.727272727272</v>
+        <v>-15.419201269505</v>
       </c>
       <c r="M24" s="15">
-        <v>15.102888427411</v>
+        <v>13.545180188176</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>284</v>
+        <v>232</v>
       </c>
       <c r="D25" s="14">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="E25" s="15">
-        <v>-5.647840531561</v>
+        <v>-27.044025157232</v>
       </c>
       <c r="F25" s="14">
-        <v>1097</v>
+        <v>1072</v>
       </c>
       <c r="G25" s="14">
-        <v>1146</v>
+        <v>1174</v>
       </c>
       <c r="H25" s="15">
-        <v>-4.275741710296</v>
+        <v>-8.688245315161</v>
       </c>
       <c r="I25" s="14">
-        <v>4743</v>
+        <v>4975</v>
       </c>
       <c r="J25" s="14">
-        <v>5387</v>
+        <v>5705</v>
       </c>
       <c r="K25" s="15">
-        <v>-11.954705773157</v>
+        <v>-12.795793163891</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.601174934725</v>
+        <v>-22.975692831707</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D26" s="14">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E26" s="15">
-        <v>-15.596330275229</v>
+        <v>36.708860759493</v>
       </c>
       <c r="F26" s="14">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="G26" s="14">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="H26" s="15">
-        <v>2.518891687657</v>
+        <v>7.751937984496</v>
       </c>
       <c r="I26" s="14">
-        <v>1626</v>
+        <v>1733</v>
       </c>
       <c r="J26" s="14">
-        <v>1614</v>
+        <v>1693</v>
       </c>
       <c r="K26" s="15">
-        <v>0.743494423791</v>
+        <v>2.362669816893</v>
       </c>
       <c r="L26" s="15">
-        <v>1.752190237797</v>
+        <v>2.121390689451</v>
       </c>
       <c r="M26" s="15">
-        <v>34.158415841584</v>
+        <v>35.708692247455</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F27" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G27" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H27" s="15">
-        <v>-9.090909090909</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I27" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J27" s="14">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K27" s="15">
-        <v>-21.176470588235</v>
+        <v>-22.826086956521</v>
       </c>
       <c r="L27" s="15">
-        <v>-11.842105263157</v>
+        <v>-11.25</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D28" s="14">
         <v>25</v>
       </c>
       <c r="E28" s="15">
-        <v>-16</v>
+        <v>16</v>
       </c>
       <c r="F28" s="14">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="G28" s="14">
         <v>88</v>
       </c>
       <c r="H28" s="15">
-        <v>-15.909090909090</v>
+        <v>2.272727272727</v>
       </c>
       <c r="I28" s="14">
-        <v>273</v>
+        <v>302</v>
       </c>
       <c r="J28" s="14">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="K28" s="15">
-        <v>-9</v>
+        <v>-7.076923076923</v>
       </c>
       <c r="L28" s="15">
-        <v>-5.536332179930</v>
+        <v>-0.983606557377</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="14">
         <v>1</v>
@@ -1476,36 +1476,36 @@
         <v>0</v>
       </c>
       <c r="F29" s="14">
+        <v>6</v>
+      </c>
+      <c r="G29" s="14">
+        <v>2</v>
+      </c>
+      <c r="H29" s="15">
+        <v>200</v>
+      </c>
+      <c r="I29" s="14">
+        <v>8</v>
+      </c>
+      <c r="J29" s="14">
         <v>5</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>400</v>
-      </c>
-      <c r="I29" s="14">
-        <v>7</v>
-      </c>
-      <c r="J29" s="14">
-        <v>4</v>
-      </c>
       <c r="K29" s="15">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="L29" s="15">
-        <v>-36.363636363636</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-41.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-87.5</v>
+        <v>-86.206896551724</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="14">
         <v>1</v>
@@ -1517,77 +1517,77 @@
         <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="I30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L30" s="15">
-        <v>-33.333333333333</v>
+        <v>-30</v>
       </c>
       <c r="M30" s="15">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="N30" s="15">
-        <v>-87.755102040816</v>
+        <v>-86.274509803921</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+        <v>37</v>
+      </c>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F31" s="14">
         <v>5</v>
       </c>
       <c r="G31" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H31" s="15">
-        <v>-37.5</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I31" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J31" s="14">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K31" s="15">
-        <v>-34.042553191489</v>
+        <v>-31.25</v>
       </c>
       <c r="L31" s="15">
-        <v>-40.384615384615</v>
+        <v>-44.067796610169</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -1605,16 +1605,16 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1638,10 +1638,10 @@
         <v>-25</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>207</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C41" s="14">
         <v>14866</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C42" s="14">
         <v>3997</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C43" s="14">
         <v>16090</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C44" s="14">
         <v>44811</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C45" s="14">
         <v>9446</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C46" s="17">
         <v>89541</v>
